--- a/research/traditional_assets/database/data/lithuania/lithuania_retail_distributors.xlsx
+++ b/research/traditional_assets/database/data/lithuania/lithuania_retail_distributors.xlsx
@@ -1272,7 +1272,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1409,22 +1409,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.07739148934563975</v>
+        <v>0.07731365211162128</v>
       </c>
       <c r="C2">
-        <v>23.68187889278619</v>
+        <v>23.51545719671121</v>
       </c>
       <c r="D2">
-        <v>23.67587889278619</v>
+        <v>23.73435719671121</v>
       </c>
       <c r="E2">
-        <v>-6.59</v>
+        <v>-6.3651</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>0.2249</v>
       </c>
       <c r="G2">
         <v>0.006</v>
@@ -1445,28 +1445,28 @@
         <v>1.816530612244898</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>0.01131247</v>
       </c>
       <c r="N2">
-        <v>1.816530612244898</v>
+        <v>1.805218142244898</v>
       </c>
       <c r="O2">
-        <v>0.2724795918367347</v>
+        <v>0.2707827213367347</v>
       </c>
       <c r="P2">
-        <v>1.544051020408163</v>
+        <v>1.534435420908163</v>
       </c>
       <c r="Q2">
-        <v>2.054051020408163</v>
+        <v>2.044435420908163</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.07739148934563975</v>
+        <v>0.07766272940567806</v>
       </c>
       <c r="T2">
-        <v>0.5786092218381922</v>
+        <v>0.5835770787933685</v>
       </c>
       <c r="U2">
         <v>0.0503</v>
@@ -1483,7 +1483,7 @@
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>160.5777175316176</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1491,22 +1491,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.07731365211162128</v>
+        <v>0.07723581487760282</v>
       </c>
       <c r="C3">
-        <v>23.51545719671121</v>
+        <v>23.34932509322005</v>
       </c>
       <c r="D3">
-        <v>23.73435719671121</v>
+        <v>23.79312509322005</v>
       </c>
       <c r="E3">
-        <v>-6.3651</v>
+        <v>-6.1402</v>
       </c>
       <c r="F3">
-        <v>0.2249</v>
+        <v>0.4498</v>
       </c>
       <c r="G3">
         <v>0.006</v>
@@ -1527,28 +1527,28 @@
         <v>1.816530612244898</v>
       </c>
       <c r="M3">
-        <v>0.01131247</v>
+        <v>0.02262494</v>
       </c>
       <c r="N3">
-        <v>1.805218142244898</v>
+        <v>1.793905672244898</v>
       </c>
       <c r="O3">
-        <v>0.2707827213367347</v>
+        <v>0.2690858508367347</v>
       </c>
       <c r="P3">
-        <v>1.534435420908163</v>
+        <v>1.524819821408163</v>
       </c>
       <c r="Q3">
-        <v>2.044435420908163</v>
+        <v>2.034819821408163</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.07766272940567806</v>
+        <v>0.07793950497714575</v>
       </c>
       <c r="T3">
-        <v>0.5835770787933685</v>
+        <v>0.5886463205843649</v>
       </c>
       <c r="U3">
         <v>0.0503</v>
@@ -1565,7 +1565,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>160.5777175316176</v>
+        <v>80.2888587658088</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1573,22 +1573,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.07723581487760282</v>
+        <v>0.07715797764358436</v>
       </c>
       <c r="C4">
-        <v>23.34932509322005</v>
+        <v>23.18348473880566</v>
       </c>
       <c r="D4">
-        <v>23.79312509322005</v>
+        <v>23.85218473880566</v>
       </c>
       <c r="E4">
-        <v>-6.1402</v>
+        <v>-5.9153</v>
       </c>
       <c r="F4">
-        <v>0.4498</v>
+        <v>0.6747000000000001</v>
       </c>
       <c r="G4">
         <v>0.006</v>
@@ -1609,28 +1609,28 @@
         <v>1.816530612244898</v>
       </c>
       <c r="M4">
-        <v>0.02262494</v>
+        <v>0.03393741</v>
       </c>
       <c r="N4">
-        <v>1.793905672244898</v>
+        <v>1.782593202244898</v>
       </c>
       <c r="O4">
-        <v>0.2690858508367347</v>
+        <v>0.2673889803367347</v>
       </c>
       <c r="P4">
-        <v>1.524819821408163</v>
+        <v>1.515204221908163</v>
       </c>
       <c r="Q4">
-        <v>2.034819821408163</v>
+        <v>2.025204221908163</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.07793950497714575</v>
+        <v>0.07822198726142718</v>
       </c>
       <c r="T4">
-        <v>0.5886463205843649</v>
+        <v>0.59382008282466</v>
       </c>
       <c r="U4">
         <v>0.0503</v>
@@ -1647,7 +1647,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>80.2888587658088</v>
+        <v>53.52590584387253</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1655,22 +1655,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.07715797764358436</v>
+        <v>0.07708014040956591</v>
       </c>
       <c r="C5">
-        <v>23.18348473880566</v>
+        <v>23.01793831142574</v>
       </c>
       <c r="D5">
-        <v>23.85218473880566</v>
+        <v>23.91153831142574</v>
       </c>
       <c r="E5">
-        <v>-5.9153</v>
+        <v>-5.690399999999999</v>
       </c>
       <c r="F5">
-        <v>0.6747000000000001</v>
+        <v>0.8996000000000001</v>
       </c>
       <c r="G5">
         <v>0.006</v>
@@ -1691,28 +1691,28 @@
         <v>1.816530612244898</v>
       </c>
       <c r="M5">
-        <v>0.03393741</v>
+        <v>0.04524988</v>
       </c>
       <c r="N5">
-        <v>1.782593202244898</v>
+        <v>1.771280732244898</v>
       </c>
       <c r="O5">
-        <v>0.2673889803367347</v>
+        <v>0.2656921098367347</v>
       </c>
       <c r="P5">
-        <v>1.515204221908163</v>
+        <v>1.505588622408163</v>
       </c>
       <c r="Q5">
-        <v>2.025204221908163</v>
+        <v>2.015588622408163</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.07822198726142718</v>
+        <v>0.07851035459329783</v>
       </c>
       <c r="T5">
-        <v>0.59382008282466</v>
+        <v>0.5991016317782948</v>
       </c>
       <c r="U5">
         <v>0.0503</v>
@@ -1729,7 +1729,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>53.52590584387253</v>
+        <v>40.1444293829044</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1737,22 +1737,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.07708014040956591</v>
+        <v>0.07700230317554745</v>
       </c>
       <c r="C6">
-        <v>23.01793831142574</v>
+        <v>22.85268801077058</v>
       </c>
       <c r="D6">
-        <v>23.91153831142574</v>
+        <v>23.97118801077059</v>
       </c>
       <c r="E6">
-        <v>-5.690399999999999</v>
+        <v>-5.4655</v>
       </c>
       <c r="F6">
-        <v>0.8996000000000001</v>
+        <v>1.1245</v>
       </c>
       <c r="G6">
         <v>0.006</v>
@@ -1773,28 +1773,28 @@
         <v>1.816530612244898</v>
       </c>
       <c r="M6">
-        <v>0.04524988</v>
+        <v>0.05656235</v>
       </c>
       <c r="N6">
-        <v>1.771280732244898</v>
+        <v>1.759968262244898</v>
       </c>
       <c r="O6">
-        <v>0.2656921098367347</v>
+        <v>0.2639952393367347</v>
       </c>
       <c r="P6">
-        <v>1.505588622408163</v>
+        <v>1.495973022908163</v>
       </c>
       <c r="Q6">
-        <v>2.015588622408163</v>
+        <v>2.005973022908163</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.07851035459329783</v>
+        <v>0.07880479281636574</v>
       </c>
       <c r="T6">
-        <v>0.5991016317782948</v>
+        <v>0.6044943712362166</v>
       </c>
       <c r="U6">
         <v>0.0503</v>
@@ -1811,7 +1811,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>40.1444293829044</v>
+        <v>32.11554350632352</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1819,22 +1819,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.07700230317554745</v>
+        <v>0.076924465941529</v>
       </c>
       <c r="C7">
-        <v>22.85268801077058</v>
+        <v>22.68773605853467</v>
       </c>
       <c r="D7">
-        <v>23.97118801077059</v>
+        <v>24.03113605853467</v>
       </c>
       <c r="E7">
-        <v>-5.4655</v>
+        <v>-5.2406</v>
       </c>
       <c r="F7">
-        <v>1.1245</v>
+        <v>1.3494</v>
       </c>
       <c r="G7">
         <v>0.006</v>
@@ -1855,28 +1855,28 @@
         <v>1.816530612244898</v>
       </c>
       <c r="M7">
-        <v>0.05656235</v>
+        <v>0.06787482</v>
       </c>
       <c r="N7">
-        <v>1.759968262244898</v>
+        <v>1.748655792244898</v>
       </c>
       <c r="O7">
-        <v>0.2639952393367347</v>
+        <v>0.2622983688367347</v>
       </c>
       <c r="P7">
-        <v>1.495973022908163</v>
+        <v>1.486357423408163</v>
       </c>
       <c r="Q7">
-        <v>2.005973022908163</v>
+        <v>1.996357423408163</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.07880479281636574</v>
+        <v>0.07910549568247766</v>
       </c>
       <c r="T7">
-        <v>0.6044943712362166</v>
+        <v>0.6100018498315409</v>
       </c>
       <c r="U7">
         <v>0.0503</v>
@@ -1893,7 +1893,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>32.11554350632352</v>
+        <v>26.76295292193626</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -1901,22 +1901,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.07692446594152899</v>
+        <v>0.07684662870751055</v>
       </c>
       <c r="C8">
-        <v>22.68773605853468</v>
+        <v>22.52308469869266</v>
       </c>
       <c r="D8">
-        <v>24.03113605853468</v>
+        <v>24.09138469869266</v>
       </c>
       <c r="E8">
-        <v>-5.2406</v>
+        <v>-5.0157</v>
       </c>
       <c r="F8">
-        <v>1.3494</v>
+        <v>1.5743</v>
       </c>
       <c r="G8">
         <v>0.006</v>
@@ -1937,28 +1937,28 @@
         <v>1.816530612244898</v>
       </c>
       <c r="M8">
-        <v>0.06787482</v>
+        <v>0.07918728999999999</v>
       </c>
       <c r="N8">
-        <v>1.748655792244898</v>
+        <v>1.737343322244898</v>
       </c>
       <c r="O8">
-        <v>0.2622983688367347</v>
+        <v>0.2606014983367347</v>
       </c>
       <c r="P8">
-        <v>1.486357423408163</v>
+        <v>1.476741823908164</v>
       </c>
       <c r="Q8">
-        <v>1.996357423408163</v>
+        <v>1.986741823908163</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.07910549568247766</v>
+        <v>0.07941266527689306</v>
       </c>
       <c r="T8">
-        <v>0.6100018498315409</v>
+        <v>0.6156277688267647</v>
       </c>
       <c r="U8">
         <v>0.0503</v>
@@ -1975,7 +1975,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>26.76295292193626</v>
+        <v>22.93967393308823</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -1983,22 +1983,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.07684662870751055</v>
+        <v>0.07676879147349208</v>
       </c>
       <c r="C9">
-        <v>22.52308469869266</v>
+        <v>22.35873619777928</v>
       </c>
       <c r="D9">
-        <v>24.09138469869266</v>
+        <v>24.15193619777928</v>
       </c>
       <c r="E9">
-        <v>-5.0157</v>
+        <v>-4.7908</v>
       </c>
       <c r="F9">
-        <v>1.5743</v>
+        <v>1.7992</v>
       </c>
       <c r="G9">
         <v>0.006</v>
@@ -2019,28 +2019,28 @@
         <v>1.816530612244898</v>
       </c>
       <c r="M9">
-        <v>0.07918729000000001</v>
+        <v>0.09049976</v>
       </c>
       <c r="N9">
-        <v>1.737343322244898</v>
+        <v>1.726030852244898</v>
       </c>
       <c r="O9">
-        <v>0.2606014983367347</v>
+        <v>0.2589046278367347</v>
       </c>
       <c r="P9">
-        <v>1.476741823908164</v>
+        <v>1.467126224408164</v>
       </c>
       <c r="Q9">
-        <v>1.986741823908163</v>
+        <v>1.977126224408163</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.07941266527689306</v>
+        <v>0.07972651247118703</v>
       </c>
       <c r="T9">
-        <v>0.6156277688267647</v>
+        <v>0.6213759904088412</v>
       </c>
       <c r="U9">
         <v>0.0503</v>
@@ -2057,7 +2057,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>22.93967393308823</v>
+        <v>20.0722146914522</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2065,22 +2065,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.07676879147349208</v>
+        <v>0.07669095423947361</v>
       </c>
       <c r="C10">
-        <v>22.35873619777928</v>
+        <v>22.19469284517361</v>
       </c>
       <c r="D10">
-        <v>24.15193619777928</v>
+        <v>24.21279284517361</v>
       </c>
       <c r="E10">
-        <v>-4.7908</v>
+        <v>-4.565899999999999</v>
       </c>
       <c r="F10">
-        <v>1.7992</v>
+        <v>2.0241</v>
       </c>
       <c r="G10">
         <v>0.006</v>
@@ -2101,28 +2101,28 @@
         <v>1.816530612244898</v>
       </c>
       <c r="M10">
-        <v>0.09049976</v>
+        <v>0.10181223</v>
       </c>
       <c r="N10">
-        <v>1.726030852244898</v>
+        <v>1.714718382244898</v>
       </c>
       <c r="O10">
-        <v>0.2589046278367347</v>
+        <v>0.2572077573367347</v>
       </c>
       <c r="P10">
-        <v>1.467126224408164</v>
+        <v>1.457510624908164</v>
       </c>
       <c r="Q10">
-        <v>1.977126224408163</v>
+        <v>1.967510624908163</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.07972651247118703</v>
+        <v>0.08004725740601495</v>
       </c>
       <c r="T10">
-        <v>0.6213759904088412</v>
+        <v>0.6272505465311831</v>
       </c>
       <c r="U10">
         <v>0.0503</v>
@@ -2139,7 +2139,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>20.0722146914522</v>
+        <v>17.84196861462418</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2147,22 +2147,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.07669095423947361</v>
+        <v>0.07661311700545516</v>
       </c>
       <c r="C11">
-        <v>22.19469284517361</v>
+        <v>22.03095695338753</v>
       </c>
       <c r="D11">
-        <v>24.21279284517361</v>
+        <v>24.27395695338753</v>
       </c>
       <c r="E11">
-        <v>-4.565899999999999</v>
+        <v>-4.340999999999999</v>
       </c>
       <c r="F11">
-        <v>2.0241</v>
+        <v>2.249</v>
       </c>
       <c r="G11">
         <v>0.006</v>
@@ -2183,28 +2183,28 @@
         <v>1.816530612244898</v>
       </c>
       <c r="M11">
-        <v>0.10181223</v>
+        <v>0.1131247</v>
       </c>
       <c r="N11">
-        <v>1.714718382244898</v>
+        <v>1.703405912244898</v>
       </c>
       <c r="O11">
-        <v>0.2572077573367347</v>
+        <v>0.2555108868367347</v>
       </c>
       <c r="P11">
-        <v>1.457510624908164</v>
+        <v>1.447895025408164</v>
       </c>
       <c r="Q11">
-        <v>1.967510624908163</v>
+        <v>1.957895025408163</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.08004725740601495</v>
+        <v>0.08037513000606128</v>
       </c>
       <c r="T11">
-        <v>0.6272505465311831</v>
+        <v>0.6332556483451326</v>
       </c>
       <c r="U11">
         <v>0.0503</v>
@@ -2221,7 +2221,7 @@
         </is>
       </c>
       <c r="Y11">
-        <v>17.84196861462418</v>
+        <v>16.05777175316176</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2229,22 +2229,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.07661311700545516</v>
+        <v>0.07653527977143669</v>
       </c>
       <c r="C12">
-        <v>22.03095695338753</v>
+        <v>21.86753085835881</v>
       </c>
       <c r="D12">
-        <v>24.27395695338753</v>
+        <v>24.33543085835881</v>
       </c>
       <c r="E12">
-        <v>-4.340999999999999</v>
+        <v>-4.116099999999999</v>
       </c>
       <c r="F12">
-        <v>2.249</v>
+        <v>2.4739</v>
       </c>
       <c r="G12">
         <v>0.006</v>
@@ -2265,28 +2265,28 @@
         <v>1.816530612244898</v>
       </c>
       <c r="M12">
-        <v>0.1131247</v>
+        <v>0.12443717</v>
       </c>
       <c r="N12">
-        <v>1.703405912244898</v>
+        <v>1.692093442244898</v>
       </c>
       <c r="O12">
-        <v>0.2555108868367347</v>
+        <v>0.2538140163367347</v>
       </c>
       <c r="P12">
-        <v>1.447895025408164</v>
+        <v>1.438279425908163</v>
       </c>
       <c r="Q12">
-        <v>1.957895025408163</v>
+        <v>1.948279425908163</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.08037513000606128</v>
+        <v>0.08071037052970415</v>
       </c>
       <c r="T12">
-        <v>0.6332556483451326</v>
+        <v>0.6393956962672607</v>
       </c>
       <c r="U12">
         <v>0.0503</v>
@@ -2303,7 +2303,7 @@
         </is>
       </c>
       <c r="Y12">
-        <v>16.05777175316176</v>
+        <v>14.59797432105614</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2311,22 +2311,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.07653527977143669</v>
+        <v>0.07645744253741824</v>
       </c>
       <c r="C13">
-        <v>21.86753085835881</v>
+        <v>21.70441691974832</v>
       </c>
       <c r="D13">
-        <v>24.33543085835881</v>
+        <v>24.39721691974832</v>
       </c>
       <c r="E13">
-        <v>-4.116099999999999</v>
+        <v>-3.8912</v>
       </c>
       <c r="F13">
-        <v>2.4739</v>
+        <v>2.6988</v>
       </c>
       <c r="G13">
         <v>0.006</v>
@@ -2347,28 +2347,28 @@
         <v>1.816530612244898</v>
       </c>
       <c r="M13">
-        <v>0.12443717</v>
+        <v>0.13574964</v>
       </c>
       <c r="N13">
-        <v>1.692093442244898</v>
+        <v>1.680780972244898</v>
       </c>
       <c r="O13">
-        <v>0.2538140163367347</v>
+        <v>0.2521171458367347</v>
       </c>
       <c r="P13">
-        <v>1.438279425908163</v>
+        <v>1.428663826408163</v>
       </c>
       <c r="Q13">
-        <v>1.948279425908163</v>
+        <v>1.938663826408163</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.08071037052970415</v>
+        <v>0.08105323015615709</v>
       </c>
       <c r="T13">
-        <v>0.6393956962672607</v>
+        <v>0.6456752907330736</v>
       </c>
       <c r="U13">
         <v>0.0503</v>
@@ -2385,7 +2385,7 @@
         </is>
       </c>
       <c r="Y13">
-        <v>14.59797432105614</v>
+        <v>13.38147646096813</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2393,22 +2393,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.07645744253741824</v>
+        <v>0.07654535530339979</v>
       </c>
       <c r="C14">
-        <v>21.70441691974832</v>
+        <v>21.40975591680978</v>
       </c>
       <c r="D14">
-        <v>24.39721691974832</v>
+        <v>24.32745591680978</v>
       </c>
       <c r="E14">
-        <v>-3.8912</v>
+        <v>-3.6663</v>
       </c>
       <c r="F14">
-        <v>2.6988</v>
+        <v>2.9237</v>
       </c>
       <c r="G14">
         <v>0.006</v>
@@ -2429,45 +2429,45 @@
         <v>1.816530612244898</v>
       </c>
       <c r="M14">
-        <v>0.13574964</v>
+        <v>0.15144766</v>
       </c>
       <c r="N14">
-        <v>1.680780972244898</v>
+        <v>1.665082952244898</v>
       </c>
       <c r="O14">
-        <v>0.2521171458367347</v>
+        <v>0.2497624428367347</v>
       </c>
       <c r="P14">
-        <v>1.428663826408163</v>
+        <v>1.415320509408163</v>
       </c>
       <c r="Q14">
-        <v>1.938663826408163</v>
+        <v>1.925320509408163</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.08105323015615709</v>
+        <v>0.0814039716131032</v>
       </c>
       <c r="T14">
-        <v>0.6456752907330736</v>
+        <v>0.6520992436923534</v>
       </c>
       <c r="U14">
-        <v>0.0503</v>
+        <v>0.0518</v>
       </c>
       <c r="V14">
         <v>0.15</v>
       </c>
       <c r="W14">
-        <v>0.04275499999999999</v>
+        <v>0.04403</v>
       </c>
       <c r="X14" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y14">
-        <v>13.38147646096813</v>
+        <v>11.99444489432783</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2475,22 +2475,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.07654535530339979</v>
+        <v>0.07648026806938131</v>
       </c>
       <c r="C15">
-        <v>21.40975591680978</v>
+        <v>21.23646585752968</v>
       </c>
       <c r="D15">
-        <v>24.32745591680978</v>
+        <v>24.37906585752968</v>
       </c>
       <c r="E15">
-        <v>-3.6663</v>
+        <v>-3.441399999999999</v>
       </c>
       <c r="F15">
-        <v>2.9237</v>
+        <v>3.148600000000001</v>
       </c>
       <c r="G15">
         <v>0.006</v>
@@ -2511,28 +2511,28 @@
         <v>1.816530612244898</v>
       </c>
       <c r="M15">
-        <v>0.15144766</v>
+        <v>0.16309748</v>
       </c>
       <c r="N15">
-        <v>1.665082952244898</v>
+        <v>1.653433132244898</v>
       </c>
       <c r="O15">
-        <v>0.2497624428367347</v>
+        <v>0.2480149698367347</v>
       </c>
       <c r="P15">
-        <v>1.415320509408163</v>
+        <v>1.405418162408163</v>
       </c>
       <c r="Q15">
-        <v>1.925320509408163</v>
+        <v>1.915418162408163</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.0814039716131032</v>
+        <v>0.08176286984811781</v>
       </c>
       <c r="T15">
-        <v>0.6520992436923534</v>
+        <v>0.6586725909065001</v>
       </c>
       <c r="U15">
         <v>0.0518</v>
@@ -2549,7 +2549,7 @@
         </is>
       </c>
       <c r="Y15">
-        <v>11.99444489432783</v>
+        <v>11.13769883044728</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2557,22 +2557,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.07648026806938131</v>
+        <v>0.07641518083536286</v>
       </c>
       <c r="C16">
-        <v>21.23646585752968</v>
+        <v>21.06339524155825</v>
       </c>
       <c r="D16">
-        <v>24.37906585752968</v>
+        <v>24.43089524155825</v>
       </c>
       <c r="E16">
-        <v>-3.441399999999999</v>
+        <v>-3.216499999999999</v>
       </c>
       <c r="F16">
-        <v>3.148600000000001</v>
+        <v>3.373500000000001</v>
       </c>
       <c r="G16">
         <v>0.006</v>
@@ -2593,28 +2593,28 @@
         <v>1.816530612244898</v>
       </c>
       <c r="M16">
-        <v>0.16309748</v>
+        <v>0.1747473</v>
       </c>
       <c r="N16">
-        <v>1.653433132244898</v>
+        <v>1.641783312244898</v>
       </c>
       <c r="O16">
-        <v>0.2480149698367347</v>
+        <v>0.2462674968367347</v>
       </c>
       <c r="P16">
-        <v>1.405418162408163</v>
+        <v>1.395515815408163</v>
       </c>
       <c r="Q16">
-        <v>1.915418162408163</v>
+        <v>1.905515815408163</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.08176286984811781</v>
+        <v>0.08213021274748572</v>
       </c>
       <c r="T16">
-        <v>0.6586725909065001</v>
+        <v>0.665400605113921</v>
       </c>
       <c r="U16">
         <v>0.0518</v>
@@ -2631,7 +2631,7 @@
         </is>
       </c>
       <c r="Y16">
-        <v>11.13769883044728</v>
+        <v>10.39518557508412</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2639,22 +2639,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.07641518083536286</v>
+        <v>0.0765812936013444</v>
       </c>
       <c r="C17">
-        <v>21.06339524155825</v>
+        <v>20.70665271289327</v>
       </c>
       <c r="D17">
-        <v>24.43089524155825</v>
+        <v>24.29905271289327</v>
       </c>
       <c r="E17">
-        <v>-3.216499999999999</v>
+        <v>-2.9916</v>
       </c>
       <c r="F17">
-        <v>3.3735</v>
+        <v>3.5984</v>
       </c>
       <c r="G17">
         <v>0.006</v>
@@ -2675,45 +2675,45 @@
         <v>1.816530612244898</v>
       </c>
       <c r="M17">
-        <v>0.1747473</v>
+        <v>0.1925144</v>
       </c>
       <c r="N17">
-        <v>1.641783312244898</v>
+        <v>1.624016212244898</v>
       </c>
       <c r="O17">
-        <v>0.2462674968367347</v>
+        <v>0.2436024318367347</v>
       </c>
       <c r="P17">
-        <v>1.395515815408163</v>
+        <v>1.380413780408163</v>
       </c>
       <c r="Q17">
-        <v>1.905515815408163</v>
+        <v>1.890413780408163</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.08213021274748572</v>
+        <v>0.08250630190636238</v>
       </c>
       <c r="T17">
-        <v>0.665400605113921</v>
+        <v>0.6722888101358043</v>
       </c>
       <c r="U17">
-        <v>0.0518</v>
+        <v>0.0535</v>
       </c>
       <c r="V17">
         <v>0.15</v>
       </c>
       <c r="W17">
-        <v>0.04403</v>
+        <v>0.04547499999999999</v>
       </c>
       <c r="X17" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y17">
-        <v>10.39518557508412</v>
+        <v>9.435816812897622</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2721,22 +2721,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.0765812936013444</v>
+        <v>0.07653065636732592</v>
       </c>
       <c r="C18">
-        <v>20.70665271289327</v>
+        <v>20.52179210560726</v>
       </c>
       <c r="D18">
-        <v>24.29905271289327</v>
+        <v>24.33909210560726</v>
       </c>
       <c r="E18">
-        <v>-2.9916</v>
+        <v>-2.766699999999999</v>
       </c>
       <c r="F18">
-        <v>3.5984</v>
+        <v>3.823300000000001</v>
       </c>
       <c r="G18">
         <v>0.006</v>
@@ -2757,28 +2757,28 @@
         <v>1.816530612244898</v>
       </c>
       <c r="M18">
-        <v>0.1925144</v>
+        <v>0.20454655</v>
       </c>
       <c r="N18">
-        <v>1.624016212244898</v>
+        <v>1.611984062244898</v>
       </c>
       <c r="O18">
-        <v>0.2436024318367347</v>
+        <v>0.2417976093367347</v>
       </c>
       <c r="P18">
-        <v>1.380413780408163</v>
+        <v>1.370186452908163</v>
       </c>
       <c r="Q18">
-        <v>1.890413780408163</v>
+        <v>1.880186452908163</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.08250630190636238</v>
+        <v>0.08289145345460956</v>
       </c>
       <c r="T18">
-        <v>0.6722888101358043</v>
+        <v>0.6793429960015883</v>
       </c>
       <c r="U18">
         <v>0.0535</v>
@@ -2795,7 +2795,7 @@
         </is>
       </c>
       <c r="Y18">
-        <v>9.435816812897622</v>
+        <v>8.880768765080113</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2803,22 +2803,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.07653065636732592</v>
+        <v>0.07648001913330749</v>
       </c>
       <c r="C19">
-        <v>20.52179210560726</v>
+        <v>20.33706366799752</v>
       </c>
       <c r="D19">
-        <v>24.33909210560726</v>
+        <v>24.37926366799752</v>
       </c>
       <c r="E19">
-        <v>-2.766699999999999</v>
+        <v>-2.541799999999999</v>
       </c>
       <c r="F19">
-        <v>3.823300000000001</v>
+        <v>4.0482</v>
       </c>
       <c r="G19">
         <v>0.006</v>
@@ -2839,28 +2839,28 @@
         <v>1.816530612244898</v>
       </c>
       <c r="M19">
-        <v>0.20454655</v>
+        <v>0.2165787</v>
       </c>
       <c r="N19">
-        <v>1.611984062244898</v>
+        <v>1.599951912244898</v>
       </c>
       <c r="O19">
-        <v>0.2417976093367347</v>
+        <v>0.2399927868367347</v>
       </c>
       <c r="P19">
-        <v>1.370186452908163</v>
+        <v>1.359959125408164</v>
       </c>
       <c r="Q19">
-        <v>1.880186452908163</v>
+        <v>1.869959125408163</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.08289145345460956</v>
+        <v>0.08328599894305791</v>
       </c>
       <c r="T19">
-        <v>0.6793429960015883</v>
+        <v>0.686569235181172</v>
       </c>
       <c r="U19">
         <v>0.0535</v>
@@ -2877,7 +2877,7 @@
         </is>
       </c>
       <c r="Y19">
-        <v>8.880768765080113</v>
+        <v>8.387392722575665</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -2885,22 +2885,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.07648001913330749</v>
+        <v>0.07642938189928901</v>
       </c>
       <c r="C20">
-        <v>20.33706366799752</v>
+        <v>20.15246805558241</v>
       </c>
       <c r="D20">
-        <v>24.37926366799752</v>
+        <v>24.41956805558241</v>
       </c>
       <c r="E20">
-        <v>-2.541799999999999</v>
+        <v>-2.3169</v>
       </c>
       <c r="F20">
-        <v>4.0482</v>
+        <v>4.2731</v>
       </c>
       <c r="G20">
         <v>0.006</v>
@@ -2921,28 +2921,28 @@
         <v>1.816530612244898</v>
       </c>
       <c r="M20">
-        <v>0.2165787</v>
+        <v>0.22861085</v>
       </c>
       <c r="N20">
-        <v>1.599951912244898</v>
+        <v>1.587919762244898</v>
       </c>
       <c r="O20">
-        <v>0.2399927868367347</v>
+        <v>0.2381879643367347</v>
       </c>
       <c r="P20">
-        <v>1.359959125408164</v>
+        <v>1.349731797908163</v>
       </c>
       <c r="Q20">
-        <v>1.869959125408163</v>
+        <v>1.859731797908163</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.08328599894305791</v>
+        <v>0.08369028629541853</v>
       </c>
       <c r="T20">
-        <v>0.686569235181172</v>
+        <v>0.6939739000195106</v>
       </c>
       <c r="U20">
         <v>0.0535</v>
@@ -2959,7 +2959,7 @@
         </is>
       </c>
       <c r="Y20">
-        <v>8.387392722575665</v>
+        <v>7.945951000334841</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -2967,22 +2967,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.07642938189928901</v>
+        <v>0.07651474466527057</v>
       </c>
       <c r="C21">
-        <v>20.15246805558241</v>
+        <v>19.85970091567887</v>
       </c>
       <c r="D21">
-        <v>24.41956805558241</v>
+        <v>24.35170091567887</v>
       </c>
       <c r="E21">
-        <v>-2.3169</v>
+        <v>-2.092</v>
       </c>
       <c r="F21">
-        <v>4.2731</v>
+        <v>4.498</v>
       </c>
       <c r="G21">
         <v>0.006</v>
@@ -3003,45 +3003,45 @@
         <v>1.816530612244898</v>
       </c>
       <c r="M21">
-        <v>0.22861085</v>
+        <v>0.2442414</v>
       </c>
       <c r="N21">
-        <v>1.587919762244898</v>
+        <v>1.572289212244898</v>
       </c>
       <c r="O21">
-        <v>0.2381879643367347</v>
+        <v>0.2358433818367347</v>
       </c>
       <c r="P21">
-        <v>1.349731797908163</v>
+        <v>1.336445830408163</v>
       </c>
       <c r="Q21">
-        <v>1.859731797908163</v>
+        <v>1.846445830408163</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.08369028629541853</v>
+        <v>0.0841046808315882</v>
       </c>
       <c r="T21">
-        <v>0.6939739000195106</v>
+        <v>0.701563681478808</v>
       </c>
       <c r="U21">
-        <v>0.0535</v>
+        <v>0.0543</v>
       </c>
       <c r="V21">
         <v>0.15</v>
       </c>
       <c r="W21">
-        <v>0.04547499999999999</v>
+        <v>0.046155</v>
       </c>
       <c r="X21" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y21">
-        <v>7.945951000334841</v>
+        <v>7.437439403167923</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3049,22 +3049,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.07651474466527057</v>
+        <v>0.07647090743125212</v>
       </c>
       <c r="C22">
-        <v>19.85970091567887</v>
+        <v>19.66960625080567</v>
       </c>
       <c r="D22">
-        <v>24.35170091567887</v>
+        <v>24.38650625080567</v>
       </c>
       <c r="E22">
-        <v>-2.092</v>
+        <v>-1.867099999999999</v>
       </c>
       <c r="F22">
-        <v>4.498</v>
+        <v>4.722900000000001</v>
       </c>
       <c r="G22">
         <v>0.006</v>
@@ -3085,28 +3085,28 @@
         <v>1.816530612244898</v>
       </c>
       <c r="M22">
-        <v>0.2442414</v>
+        <v>0.2564534700000001</v>
       </c>
       <c r="N22">
-        <v>1.572289212244898</v>
+        <v>1.560077142244898</v>
       </c>
       <c r="O22">
-        <v>0.2358433818367347</v>
+        <v>0.2340115713367347</v>
       </c>
       <c r="P22">
-        <v>1.336445830408163</v>
+        <v>1.326065570908163</v>
       </c>
       <c r="Q22">
-        <v>1.846445830408163</v>
+        <v>1.836065570908163</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.0841046808315882</v>
+        <v>0.08452956636867355</v>
       </c>
       <c r="T22">
-        <v>0.701563681478808</v>
+        <v>0.7093456093041636</v>
       </c>
       <c r="U22">
         <v>0.0543</v>
@@ -3123,7 +3123,7 @@
         </is>
       </c>
       <c r="Y22">
-        <v>7.437439403167923</v>
+        <v>7.083275622064687</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3131,22 +3131,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.07647090743125209</v>
+        <v>0.07642707019723365</v>
       </c>
       <c r="C23">
-        <v>19.66960625080569</v>
+        <v>19.47961122129502</v>
       </c>
       <c r="D23">
-        <v>24.38650625080569</v>
+        <v>24.42141122129502</v>
       </c>
       <c r="E23">
-        <v>-1.8671</v>
+        <v>-1.642199999999999</v>
       </c>
       <c r="F23">
-        <v>4.7229</v>
+        <v>4.947800000000001</v>
       </c>
       <c r="G23">
         <v>0.006</v>
@@ -3167,28 +3167,28 @@
         <v>1.816530612244898</v>
       </c>
       <c r="M23">
-        <v>0.25645347</v>
+        <v>0.26866554</v>
       </c>
       <c r="N23">
-        <v>1.560077142244898</v>
+        <v>1.547865072244898</v>
       </c>
       <c r="O23">
-        <v>0.2340115713367347</v>
+        <v>0.2321797608367347</v>
       </c>
       <c r="P23">
-        <v>1.326065570908163</v>
+        <v>1.315685311408163</v>
       </c>
       <c r="Q23">
-        <v>1.836065570908163</v>
+        <v>1.825685311408163</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.08452956636867354</v>
+        <v>0.0849653464067098</v>
       </c>
       <c r="T23">
-        <v>0.7093456093041633</v>
+        <v>0.7173270737404255</v>
       </c>
       <c r="U23">
         <v>0.0543</v>
@@ -3205,7 +3205,7 @@
         </is>
       </c>
       <c r="Y23">
-        <v>7.083275622064688</v>
+        <v>6.761308548334475</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3213,22 +3213,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.07642707019723365</v>
+        <v>0.07638323296321518</v>
       </c>
       <c r="C24">
-        <v>19.47961122129502</v>
+        <v>19.28971625559131</v>
       </c>
       <c r="D24">
-        <v>24.42141122129502</v>
+        <v>24.45641625559131</v>
       </c>
       <c r="E24">
-        <v>-1.642199999999999</v>
+        <v>-1.417299999999999</v>
       </c>
       <c r="F24">
-        <v>4.947800000000001</v>
+        <v>5.172700000000001</v>
       </c>
       <c r="G24">
         <v>0.006</v>
@@ -3249,28 +3249,28 @@
         <v>1.816530612244898</v>
       </c>
       <c r="M24">
-        <v>0.26866554</v>
+        <v>0.2808776100000001</v>
       </c>
       <c r="N24">
-        <v>1.547865072244898</v>
+        <v>1.535653002244898</v>
       </c>
       <c r="O24">
-        <v>0.2321797608367347</v>
+        <v>0.2303479503367347</v>
       </c>
       <c r="P24">
-        <v>1.315685311408163</v>
+        <v>1.305305051908163</v>
       </c>
       <c r="Q24">
-        <v>1.825685311408163</v>
+        <v>1.815305051908163</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.0849653464067098</v>
+        <v>0.08541244540677295</v>
       </c>
       <c r="T24">
-        <v>0.7173270737404255</v>
+        <v>0.7255158489412656</v>
       </c>
       <c r="U24">
         <v>0.0543</v>
@@ -3287,7 +3287,7 @@
         </is>
       </c>
       <c r="Y24">
-        <v>6.761308548334475</v>
+        <v>6.467338611450367</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3295,22 +3295,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.07638323296321518</v>
+        <v>0.07633939572919672</v>
       </c>
       <c r="C25">
-        <v>19.28971625559131</v>
+        <v>19.09992178459903</v>
       </c>
       <c r="D25">
-        <v>24.45641625559131</v>
+        <v>24.49152178459903</v>
       </c>
       <c r="E25">
-        <v>-1.417299999999999</v>
+        <v>-1.192399999999999</v>
       </c>
       <c r="F25">
-        <v>5.172700000000001</v>
+        <v>5.397600000000001</v>
       </c>
       <c r="G25">
         <v>0.006</v>
@@ -3331,28 +3331,28 @@
         <v>1.816530612244898</v>
       </c>
       <c r="M25">
-        <v>0.2808776100000001</v>
+        <v>0.29308968</v>
       </c>
       <c r="N25">
-        <v>1.535653002244898</v>
+        <v>1.523440932244898</v>
       </c>
       <c r="O25">
-        <v>0.2303479503367347</v>
+        <v>0.2285161398367347</v>
       </c>
       <c r="P25">
-        <v>1.305305051908163</v>
+        <v>1.294924792408163</v>
       </c>
       <c r="Q25">
-        <v>1.815305051908163</v>
+        <v>1.804924792408163</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.08541244540677295</v>
+        <v>0.08587131016999569</v>
       </c>
       <c r="T25">
-        <v>0.7255158489412656</v>
+        <v>0.7339201182263385</v>
       </c>
       <c r="U25">
         <v>0.0543</v>
@@ -3369,7 +3369,7 @@
         </is>
       </c>
       <c r="Y25">
-        <v>6.467338611450367</v>
+        <v>6.197866169306603</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3377,22 +3377,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.07633939572919672</v>
+        <v>0.07650805849517826</v>
       </c>
       <c r="C26">
-        <v>19.09992178459903</v>
+        <v>18.74050309440126</v>
       </c>
       <c r="D26">
-        <v>24.49152178459903</v>
+        <v>24.35700309440126</v>
       </c>
       <c r="E26">
-        <v>-1.192399999999999</v>
+        <v>-0.9674999999999994</v>
       </c>
       <c r="F26">
-        <v>5.397600000000001</v>
+        <v>5.6225</v>
       </c>
       <c r="G26">
         <v>0.006</v>
@@ -3413,45 +3413,45 @@
         <v>1.816530612244898</v>
       </c>
       <c r="M26">
-        <v>0.29308968</v>
+        <v>0.31092425</v>
       </c>
       <c r="N26">
-        <v>1.523440932244898</v>
+        <v>1.505606362244898</v>
       </c>
       <c r="O26">
-        <v>0.2285161398367347</v>
+        <v>0.2258409543367347</v>
       </c>
       <c r="P26">
-        <v>1.294924792408163</v>
+        <v>1.279765407908163</v>
       </c>
       <c r="Q26">
-        <v>1.804924792408163</v>
+        <v>1.789765407908163</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.08587131016999569</v>
+        <v>0.08634241132690434</v>
       </c>
       <c r="T26">
-        <v>0.7339201182263385</v>
+        <v>0.7425485013590133</v>
       </c>
       <c r="U26">
-        <v>0.0543</v>
+        <v>0.0553</v>
       </c>
       <c r="V26">
         <v>0.15</v>
       </c>
       <c r="W26">
-        <v>0.046155</v>
+        <v>0.047005</v>
       </c>
       <c r="X26" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y26">
-        <v>6.197866169306603</v>
+        <v>5.842357462452344</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3459,22 +3459,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.07650805849517826</v>
+        <v>0.07647272126115981</v>
       </c>
       <c r="C27">
-        <v>18.74050309440126</v>
+        <v>18.54366415592256</v>
       </c>
       <c r="D27">
-        <v>24.35700309440126</v>
+        <v>24.38506415592256</v>
       </c>
       <c r="E27">
-        <v>-0.9674999999999994</v>
+        <v>-0.7425999999999995</v>
       </c>
       <c r="F27">
-        <v>5.6225</v>
+        <v>5.8474</v>
       </c>
       <c r="G27">
         <v>0.006</v>
@@ -3495,28 +3495,28 @@
         <v>1.816530612244898</v>
       </c>
       <c r="M27">
-        <v>0.31092425</v>
+        <v>0.32336122</v>
       </c>
       <c r="N27">
-        <v>1.505606362244898</v>
+        <v>1.493169392244898</v>
       </c>
       <c r="O27">
-        <v>0.2258409543367347</v>
+        <v>0.2239754088367347</v>
       </c>
       <c r="P27">
-        <v>1.279765407908163</v>
+        <v>1.269193983408163</v>
       </c>
       <c r="Q27">
-        <v>1.789765407908163</v>
+        <v>1.779193983408163</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.08634241132690434</v>
+        <v>0.08682624494751325</v>
       </c>
       <c r="T27">
-        <v>0.7425485013590133</v>
+        <v>0.7514100840358144</v>
       </c>
       <c r="U27">
         <v>0.0553</v>
@@ -3533,7 +3533,7 @@
         </is>
       </c>
       <c r="Y27">
-        <v>5.842357462452344</v>
+        <v>5.617651406204176</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3541,22 +3541,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.07647272126115981</v>
+        <v>0.07643738402714136</v>
       </c>
       <c r="C28">
-        <v>18.54366415592256</v>
+        <v>18.34688994883848</v>
       </c>
       <c r="D28">
-        <v>24.38506415592256</v>
+        <v>24.41318994883848</v>
       </c>
       <c r="E28">
-        <v>-0.7425999999999995</v>
+        <v>-0.5176999999999987</v>
       </c>
       <c r="F28">
-        <v>5.8474</v>
+        <v>6.072300000000001</v>
       </c>
       <c r="G28">
         <v>0.006</v>
@@ -3577,28 +3577,28 @@
         <v>1.816530612244898</v>
       </c>
       <c r="M28">
-        <v>0.32336122</v>
+        <v>0.3357981900000001</v>
       </c>
       <c r="N28">
-        <v>1.493169392244898</v>
+        <v>1.480732422244898</v>
       </c>
       <c r="O28">
-        <v>0.2239754088367347</v>
+        <v>0.2221098633367347</v>
       </c>
       <c r="P28">
-        <v>1.269193983408163</v>
+        <v>1.258622558908163</v>
       </c>
       <c r="Q28">
-        <v>1.779193983408163</v>
+        <v>1.768622558908163</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.08682624494751325</v>
+        <v>0.08732333428375527</v>
       </c>
       <c r="T28">
-        <v>0.7514100840358144</v>
+        <v>0.7605144497996513</v>
       </c>
       <c r="U28">
         <v>0.0553</v>
@@ -3615,7 +3615,7 @@
         </is>
       </c>
       <c r="Y28">
-        <v>5.617651406204176</v>
+        <v>5.409590243011428</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3623,22 +3623,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.07643738402714136</v>
+        <v>0.07640204679312289</v>
       </c>
       <c r="C29">
-        <v>18.34688994883848</v>
+        <v>18.15018069739172</v>
       </c>
       <c r="D29">
-        <v>24.41318994883848</v>
+        <v>24.44138069739172</v>
       </c>
       <c r="E29">
-        <v>-0.5176999999999987</v>
+        <v>-0.2927999999999988</v>
       </c>
       <c r="F29">
-        <v>6.072300000000001</v>
+        <v>6.297200000000001</v>
       </c>
       <c r="G29">
         <v>0.006</v>
@@ -3659,28 +3659,28 @@
         <v>1.816530612244898</v>
       </c>
       <c r="M29">
-        <v>0.3357981900000001</v>
+        <v>0.34823516</v>
       </c>
       <c r="N29">
-        <v>1.480732422244898</v>
+        <v>1.468295452244898</v>
       </c>
       <c r="O29">
-        <v>0.2221098633367347</v>
+        <v>0.2202443178367347</v>
       </c>
       <c r="P29">
-        <v>1.258622558908163</v>
+        <v>1.248051134408164</v>
       </c>
       <c r="Q29">
-        <v>1.768622558908163</v>
+        <v>1.758051134408163</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.08732333428375527</v>
+        <v>0.08783423165711512</v>
       </c>
       <c r="T29">
-        <v>0.7605144497996513</v>
+        <v>0.7698717146124836</v>
       </c>
       <c r="U29">
         <v>0.0553</v>
@@ -3697,7 +3697,7 @@
         </is>
       </c>
       <c r="Y29">
-        <v>5.409590243011428</v>
+        <v>5.216390591475307</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3705,22 +3705,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.07640204679312289</v>
+        <v>0.07636670955910443</v>
       </c>
       <c r="C30">
-        <v>18.15018069739172</v>
+        <v>17.95353662686191</v>
       </c>
       <c r="D30">
-        <v>24.44138069739172</v>
+        <v>24.46963662686191</v>
       </c>
       <c r="E30">
-        <v>-0.2927999999999988</v>
+        <v>-0.06789999999999807</v>
       </c>
       <c r="F30">
-        <v>6.297200000000001</v>
+        <v>6.522100000000002</v>
       </c>
       <c r="G30">
         <v>0.006</v>
@@ -3741,28 +3741,28 @@
         <v>1.816530612244898</v>
       </c>
       <c r="M30">
-        <v>0.34823516</v>
+        <v>0.3606721300000001</v>
       </c>
       <c r="N30">
-        <v>1.468295452244898</v>
+        <v>1.455858482244898</v>
       </c>
       <c r="O30">
-        <v>0.2202443178367347</v>
+        <v>0.2183787723367347</v>
       </c>
       <c r="P30">
-        <v>1.248051134408164</v>
+        <v>1.237479709908163</v>
       </c>
       <c r="Q30">
-        <v>1.758051134408163</v>
+        <v>1.747479709908163</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.08783423165711512</v>
+        <v>0.08835952050578089</v>
       </c>
       <c r="T30">
-        <v>0.7698717146124836</v>
+        <v>0.7794925643496209</v>
       </c>
       <c r="U30">
         <v>0.0553</v>
@@ -3779,7 +3779,7 @@
         </is>
       </c>
       <c r="Y30">
-        <v>5.216390591475307</v>
+        <v>5.036515053838226</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3787,22 +3787,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.07636670955910443</v>
+        <v>0.07633137232508597</v>
       </c>
       <c r="C31">
-        <v>17.95353662686191</v>
+        <v>17.75695796357169</v>
       </c>
       <c r="D31">
-        <v>24.46963662686191</v>
+        <v>24.49795796357169</v>
       </c>
       <c r="E31">
-        <v>-0.06789999999999985</v>
+        <v>0.1570000000000009</v>
       </c>
       <c r="F31">
-        <v>6.5221</v>
+        <v>6.747000000000001</v>
       </c>
       <c r="G31">
         <v>0.006</v>
@@ -3823,28 +3823,28 @@
         <v>1.816530612244898</v>
       </c>
       <c r="M31">
-        <v>0.36067213</v>
+        <v>0.3731091000000001</v>
       </c>
       <c r="N31">
-        <v>1.455858482244898</v>
+        <v>1.443421512244898</v>
       </c>
       <c r="O31">
-        <v>0.2183787723367347</v>
+        <v>0.2165132268367347</v>
       </c>
       <c r="P31">
-        <v>1.237479709908163</v>
+        <v>1.226908285408163</v>
       </c>
       <c r="Q31">
-        <v>1.747479709908163</v>
+        <v>1.736908285408163</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.08835952050578089</v>
+        <v>0.08889981760726567</v>
       </c>
       <c r="T31">
-        <v>0.7794925643496209</v>
+        <v>0.7893882955078194</v>
       </c>
       <c r="U31">
         <v>0.0553</v>
@@ -3861,7 +3861,7 @@
         </is>
       </c>
       <c r="Y31">
-        <v>5.036515053838227</v>
+        <v>4.868631218710285</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -3869,22 +3869,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.07633137232508597</v>
+        <v>0.0762960350910675</v>
       </c>
       <c r="C32">
-        <v>17.75695796357169</v>
+        <v>17.56044493489265</v>
       </c>
       <c r="D32">
-        <v>24.49795796357169</v>
+        <v>24.52634493489265</v>
       </c>
       <c r="E32">
-        <v>0.1570000000000009</v>
+        <v>0.3819000000000008</v>
       </c>
       <c r="F32">
-        <v>6.747000000000001</v>
+        <v>6.971900000000001</v>
       </c>
       <c r="G32">
         <v>0.006</v>
@@ -3905,28 +3905,28 @@
         <v>1.816530612244898</v>
       </c>
       <c r="M32">
-        <v>0.3731091000000001</v>
+        <v>0.3855460700000001</v>
       </c>
       <c r="N32">
-        <v>1.443421512244898</v>
+        <v>1.430984542244898</v>
       </c>
       <c r="O32">
-        <v>0.2165132268367347</v>
+        <v>0.2146476813367347</v>
       </c>
       <c r="P32">
-        <v>1.226908285408163</v>
+        <v>1.216336860908163</v>
       </c>
       <c r="Q32">
-        <v>1.736908285408163</v>
+        <v>1.726336860908163</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.08889981760726567</v>
+        <v>0.08945577549430073</v>
       </c>
       <c r="T32">
-        <v>0.7893882955078194</v>
+        <v>0.7995708594532119</v>
       </c>
       <c r="U32">
         <v>0.0553</v>
@@ -3943,7 +3943,7 @@
         </is>
       </c>
       <c r="Y32">
-        <v>4.868631218710285</v>
+        <v>4.711578598751888</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -3951,22 +3951,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.0762960350910675</v>
+        <v>0.07626069785704903</v>
       </c>
       <c r="C33">
-        <v>17.56044493489265</v>
+        <v>17.36399776925151</v>
       </c>
       <c r="D33">
-        <v>24.52634493489265</v>
+        <v>24.55479776925151</v>
       </c>
       <c r="E33">
-        <v>0.3819000000000008</v>
+        <v>0.6068000000000007</v>
       </c>
       <c r="F33">
-        <v>6.971900000000001</v>
+        <v>7.196800000000001</v>
       </c>
       <c r="G33">
         <v>0.006</v>
@@ -3987,28 +3987,28 @@
         <v>1.816530612244898</v>
       </c>
       <c r="M33">
-        <v>0.3855460700000001</v>
+        <v>0.3979830400000001</v>
       </c>
       <c r="N33">
-        <v>1.430984542244898</v>
+        <v>1.418547572244898</v>
       </c>
       <c r="O33">
-        <v>0.2146476813367347</v>
+        <v>0.2127821358367347</v>
       </c>
       <c r="P33">
-        <v>1.216336860908163</v>
+        <v>1.205765436408163</v>
       </c>
       <c r="Q33">
-        <v>1.726336860908163</v>
+        <v>1.715765436408163</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.08945577549430073</v>
+        <v>0.09002808508389565</v>
       </c>
       <c r="T33">
-        <v>0.7995708594532119</v>
+        <v>0.8100529105734691</v>
       </c>
       <c r="U33">
         <v>0.0553</v>
@@ -4025,7 +4025,7 @@
         </is>
       </c>
       <c r="Y33">
-        <v>4.711578598751888</v>
+        <v>4.564341767540892</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4033,22 +4033,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.07626069785704903</v>
+        <v>0.07692661062303058</v>
       </c>
       <c r="C34">
-        <v>17.36399776925151</v>
+        <v>16.61378026845875</v>
       </c>
       <c r="D34">
-        <v>24.55479776925151</v>
+        <v>24.02948026845875</v>
       </c>
       <c r="E34">
-        <v>0.6068000000000007</v>
+        <v>0.8317000000000014</v>
       </c>
       <c r="F34">
-        <v>7.196800000000001</v>
+        <v>7.421700000000001</v>
       </c>
       <c r="G34">
         <v>0.006</v>
@@ -4069,45 +4069,45 @@
         <v>1.816530612244898</v>
       </c>
       <c r="M34">
-        <v>0.3979830400000001</v>
+        <v>0.4289742600000001</v>
       </c>
       <c r="N34">
-        <v>1.418547572244898</v>
+        <v>1.387556352244898</v>
       </c>
       <c r="O34">
-        <v>0.2127821358367347</v>
+        <v>0.2081334528367347</v>
       </c>
       <c r="P34">
-        <v>1.205765436408163</v>
+        <v>1.179422899408163</v>
       </c>
       <c r="Q34">
-        <v>1.715765436408163</v>
+        <v>1.689422899408163</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.09002808508389565</v>
+        <v>0.09061747854183669</v>
       </c>
       <c r="T34">
-        <v>0.8100529105734691</v>
+        <v>0.8208478587420921</v>
       </c>
       <c r="U34">
-        <v>0.0553</v>
+        <v>0.0578</v>
       </c>
       <c r="V34">
         <v>0.15</v>
       </c>
       <c r="W34">
-        <v>0.047005</v>
+        <v>0.04913</v>
       </c>
       <c r="X34" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y34">
-        <v>4.564341767540892</v>
+        <v>4.234591166949965</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4115,22 +4115,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.07692661062303058</v>
+        <v>0.07691252338901211</v>
       </c>
       <c r="C35">
-        <v>16.61378026845875</v>
+        <v>16.39976041815447</v>
       </c>
       <c r="D35">
-        <v>24.02948026845875</v>
+        <v>24.04036041815447</v>
       </c>
       <c r="E35">
-        <v>0.8317000000000014</v>
+        <v>1.056600000000001</v>
       </c>
       <c r="F35">
-        <v>7.421700000000001</v>
+        <v>7.646600000000001</v>
       </c>
       <c r="G35">
         <v>0.006</v>
@@ -4151,28 +4151,28 @@
         <v>1.816530612244898</v>
       </c>
       <c r="M35">
-        <v>0.4289742600000001</v>
+        <v>0.4419734800000001</v>
       </c>
       <c r="N35">
-        <v>1.387556352244898</v>
+        <v>1.374557132244898</v>
       </c>
       <c r="O35">
-        <v>0.2081334528367347</v>
+        <v>0.2061835698367347</v>
       </c>
       <c r="P35">
-        <v>1.179422899408163</v>
+        <v>1.168373562408163</v>
       </c>
       <c r="Q35">
-        <v>1.689422899408163</v>
+        <v>1.678373562408163</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.09061747854183669</v>
+        <v>0.09122473240759413</v>
       </c>
       <c r="T35">
-        <v>0.8208478587420921</v>
+        <v>0.8319699265521885</v>
       </c>
       <c r="U35">
         <v>0.0578</v>
@@ -4189,7 +4189,7 @@
         </is>
       </c>
       <c r="Y35">
-        <v>4.234591166949965</v>
+        <v>4.110044367922025</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4197,22 +4197,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.07691252338901211</v>
+        <v>0.07793968615499366</v>
       </c>
       <c r="C36">
-        <v>16.39976041815447</v>
+        <v>15.40654665854832</v>
       </c>
       <c r="D36">
-        <v>24.04036041815447</v>
+        <v>23.27204665854832</v>
       </c>
       <c r="E36">
-        <v>1.056600000000001</v>
+        <v>1.281500000000001</v>
       </c>
       <c r="F36">
-        <v>7.646600000000001</v>
+        <v>7.871500000000001</v>
       </c>
       <c r="G36">
         <v>0.006</v>
@@ -4233,45 +4233,45 @@
         <v>1.816530612244898</v>
       </c>
       <c r="M36">
-        <v>0.4419734800000001</v>
+        <v>0.4825229500000001</v>
       </c>
       <c r="N36">
-        <v>1.374557132244898</v>
+        <v>1.334007662244898</v>
       </c>
       <c r="O36">
-        <v>0.2061835698367347</v>
+        <v>0.2001011493367347</v>
       </c>
       <c r="P36">
-        <v>1.168373562408163</v>
+        <v>1.133906512908163</v>
       </c>
       <c r="Q36">
-        <v>1.678373562408163</v>
+        <v>1.643906512908163</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.09122473240759413</v>
+        <v>0.09185067100768257</v>
       </c>
       <c r="T36">
-        <v>0.8319699265521885</v>
+        <v>0.8434342118333649</v>
       </c>
       <c r="U36">
-        <v>0.0578</v>
+        <v>0.0613</v>
       </c>
       <c r="V36">
         <v>0.15</v>
       </c>
       <c r="W36">
-        <v>0.04913</v>
+        <v>0.052105</v>
       </c>
       <c r="X36" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y36">
-        <v>4.110044367922025</v>
+        <v>3.764651219687888</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4279,22 +4279,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.07793968615499366</v>
+        <v>0.07795534892097519</v>
       </c>
       <c r="C37">
-        <v>15.40654665854832</v>
+        <v>15.17031092023554</v>
       </c>
       <c r="D37">
-        <v>23.27204665854832</v>
+        <v>23.26071092023554</v>
       </c>
       <c r="E37">
-        <v>1.281500000000001</v>
+        <v>1.506400000000001</v>
       </c>
       <c r="F37">
-        <v>7.871500000000001</v>
+        <v>8.096400000000001</v>
       </c>
       <c r="G37">
         <v>0.006</v>
@@ -4315,28 +4315,28 @@
         <v>1.816530612244898</v>
       </c>
       <c r="M37">
-        <v>0.4825229500000001</v>
+        <v>0.4963093200000001</v>
       </c>
       <c r="N37">
-        <v>1.334007662244898</v>
+        <v>1.320221292244898</v>
       </c>
       <c r="O37">
-        <v>0.2001011493367347</v>
+        <v>0.1980331938367347</v>
       </c>
       <c r="P37">
-        <v>1.133906512908163</v>
+        <v>1.122188098408163</v>
       </c>
       <c r="Q37">
-        <v>1.643906512908163</v>
+        <v>1.632188098408163</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.09185067100768257</v>
+        <v>0.09249617018902376</v>
       </c>
       <c r="T37">
-        <v>0.8434342118333649</v>
+        <v>0.855256756029578</v>
       </c>
       <c r="U37">
         <v>0.0613</v>
@@ -4353,7 +4353,7 @@
         </is>
       </c>
       <c r="Y37">
-        <v>3.764651219687888</v>
+        <v>3.660077574696558</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4361,22 +4361,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.07795534892097521</v>
+        <v>0.07797101168695675</v>
       </c>
       <c r="C38">
-        <v>15.17031092023553</v>
+        <v>14.93408621974887</v>
       </c>
       <c r="D38">
-        <v>23.26071092023554</v>
+        <v>23.24938621974887</v>
       </c>
       <c r="E38">
-        <v>1.506400000000001</v>
+        <v>1.731300000000001</v>
       </c>
       <c r="F38">
-        <v>8.096400000000001</v>
+        <v>8.321300000000001</v>
       </c>
       <c r="G38">
         <v>0.006</v>
@@ -4397,28 +4397,28 @@
         <v>1.816530612244898</v>
       </c>
       <c r="M38">
-        <v>0.4963093200000001</v>
+        <v>0.5100956900000001</v>
       </c>
       <c r="N38">
-        <v>1.320221292244898</v>
+        <v>1.306434922244898</v>
       </c>
       <c r="O38">
-        <v>0.1980331938367347</v>
+        <v>0.1959652383367347</v>
       </c>
       <c r="P38">
-        <v>1.122188098408163</v>
+        <v>1.110469683908163</v>
       </c>
       <c r="Q38">
-        <v>1.632188098408163</v>
+        <v>1.620469683908163</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.09249617018902376</v>
+        <v>0.09316216140786784</v>
       </c>
       <c r="T38">
-        <v>0.8552567560295777</v>
+        <v>0.8674546190891628</v>
       </c>
       <c r="U38">
         <v>0.0613</v>
@@ -4435,7 +4435,7 @@
         </is>
       </c>
       <c r="Y38">
-        <v>3.660077574696558</v>
+        <v>3.561156559164218</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4443,22 +4443,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.07797101168695675</v>
+        <v>0.07889107445293828</v>
       </c>
       <c r="C39">
-        <v>14.93408621974887</v>
+        <v>14.06276131676976</v>
       </c>
       <c r="D39">
-        <v>23.24938621974887</v>
+        <v>22.60296131676976</v>
       </c>
       <c r="E39">
-        <v>1.731300000000001</v>
+        <v>1.956200000000001</v>
       </c>
       <c r="F39">
-        <v>8.321300000000001</v>
+        <v>8.546200000000001</v>
       </c>
       <c r="G39">
         <v>0.006</v>
@@ -4479,45 +4479,45 @@
         <v>1.816530612244898</v>
       </c>
       <c r="M39">
-        <v>0.5100956900000001</v>
+        <v>0.54781142</v>
       </c>
       <c r="N39">
-        <v>1.306434922244898</v>
+        <v>1.268719192244898</v>
       </c>
       <c r="O39">
-        <v>0.1959652383367347</v>
+        <v>0.1903078788367347</v>
       </c>
       <c r="P39">
-        <v>1.110469683908163</v>
+        <v>1.078411313408163</v>
       </c>
       <c r="Q39">
-        <v>1.620469683908163</v>
+        <v>1.588411313408163</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.09316216140786784</v>
+        <v>0.09384963621441658</v>
       </c>
       <c r="T39">
-        <v>0.8674546190891628</v>
+        <v>0.8800459616022827</v>
       </c>
       <c r="U39">
-        <v>0.0613</v>
+        <v>0.0641</v>
       </c>
       <c r="V39">
         <v>0.15</v>
       </c>
       <c r="W39">
-        <v>0.052105</v>
+        <v>0.054485</v>
       </c>
       <c r="X39" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y39">
-        <v>3.561156559164218</v>
+        <v>3.315977991559391</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4525,22 +4525,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.07889107445293828</v>
+        <v>0.07893053721891982</v>
       </c>
       <c r="C40">
-        <v>14.06276131676976</v>
+        <v>13.81093825883563</v>
       </c>
       <c r="D40">
-        <v>22.60296131676976</v>
+        <v>22.57603825883563</v>
       </c>
       <c r="E40">
-        <v>1.956200000000001</v>
+        <v>2.181100000000001</v>
       </c>
       <c r="F40">
-        <v>8.546200000000001</v>
+        <v>8.771100000000001</v>
       </c>
       <c r="G40">
         <v>0.006</v>
@@ -4561,28 +4561,28 @@
         <v>1.816530612244898</v>
       </c>
       <c r="M40">
-        <v>0.54781142</v>
+        <v>0.56222751</v>
       </c>
       <c r="N40">
-        <v>1.268719192244898</v>
+        <v>1.254303102244898</v>
       </c>
       <c r="O40">
-        <v>0.1903078788367347</v>
+        <v>0.1881454653367347</v>
       </c>
       <c r="P40">
-        <v>1.078411313408163</v>
+        <v>1.066157636908163</v>
       </c>
       <c r="Q40">
-        <v>1.588411313408163</v>
+        <v>1.576157636908163</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.09384963621441658</v>
+        <v>0.09455965117855708</v>
       </c>
       <c r="T40">
-        <v>0.8800459616022827</v>
+        <v>0.893050135017472</v>
       </c>
       <c r="U40">
         <v>0.0641</v>
@@ -4599,7 +4599,7 @@
         </is>
       </c>
       <c r="Y40">
-        <v>3.315977991559391</v>
+        <v>3.23095291485274</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4607,22 +4607,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.07893053721891982</v>
+        <v>0.07896999998490137</v>
       </c>
       <c r="C41">
-        <v>13.81093825883563</v>
+        <v>13.55917926230249</v>
       </c>
       <c r="D41">
-        <v>22.57603825883563</v>
+        <v>22.54917926230249</v>
       </c>
       <c r="E41">
-        <v>2.181100000000001</v>
+        <v>2.406000000000001</v>
       </c>
       <c r="F41">
-        <v>8.771100000000001</v>
+        <v>8.996</v>
       </c>
       <c r="G41">
         <v>0.006</v>
@@ -4643,28 +4643,28 @@
         <v>1.816530612244898</v>
       </c>
       <c r="M41">
-        <v>0.56222751</v>
+        <v>0.5766436</v>
       </c>
       <c r="N41">
-        <v>1.254303102244898</v>
+        <v>1.239887012244898</v>
       </c>
       <c r="O41">
-        <v>0.1881454653367347</v>
+        <v>0.1859830518367347</v>
       </c>
       <c r="P41">
-        <v>1.066157636908163</v>
+        <v>1.053903960408163</v>
       </c>
       <c r="Q41">
-        <v>1.576157636908163</v>
+        <v>1.563903960408163</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.09455965117855708</v>
+        <v>0.09529333330816894</v>
       </c>
       <c r="T41">
-        <v>0.893050135017472</v>
+        <v>0.9064877808798345</v>
       </c>
       <c r="U41">
         <v>0.0641</v>
@@ -4681,7 +4681,7 @@
         </is>
       </c>
       <c r="Y41">
-        <v>3.23095291485274</v>
+        <v>3.150179091981421</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4689,22 +4689,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.07896999998490137</v>
+        <v>0.07900946275088291</v>
       </c>
       <c r="C42">
-        <v>13.55917926230249</v>
+        <v>13.30748409879806</v>
       </c>
       <c r="D42">
-        <v>22.54917926230249</v>
+        <v>22.52238409879806</v>
       </c>
       <c r="E42">
-        <v>2.406000000000001</v>
+        <v>2.630900000000002</v>
       </c>
       <c r="F42">
-        <v>8.996</v>
+        <v>9.220900000000002</v>
       </c>
       <c r="G42">
         <v>0.006</v>
@@ -4725,28 +4725,28 @@
         <v>1.816530612244898</v>
       </c>
       <c r="M42">
-        <v>0.5766436</v>
+        <v>0.5910596900000001</v>
       </c>
       <c r="N42">
-        <v>1.239887012244898</v>
+        <v>1.225470922244898</v>
       </c>
       <c r="O42">
-        <v>0.1859830518367347</v>
+        <v>0.1838206383367347</v>
       </c>
       <c r="P42">
-        <v>1.053903960408163</v>
+        <v>1.041650283908163</v>
       </c>
       <c r="Q42">
-        <v>1.563903960408163</v>
+        <v>1.551650283908163</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.09529333330816894</v>
+        <v>0.09605188601844561</v>
       </c>
       <c r="T42">
-        <v>0.9064877808798345</v>
+        <v>0.92038094016126</v>
       </c>
       <c r="U42">
         <v>0.0641</v>
@@ -4763,7 +4763,7 @@
         </is>
       </c>
       <c r="Y42">
-        <v>3.150179091981421</v>
+        <v>3.07334545559163</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4771,22 +4771,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.07900946275088291</v>
+        <v>0.07904892551686445</v>
       </c>
       <c r="C43">
-        <v>13.30748409879806</v>
+        <v>13.0558525410343</v>
       </c>
       <c r="D43">
-        <v>22.52238409879806</v>
+        <v>22.4956525410343</v>
       </c>
       <c r="E43">
-        <v>2.630900000000002</v>
+        <v>2.855800000000002</v>
       </c>
       <c r="F43">
-        <v>9.220900000000002</v>
+        <v>9.445800000000002</v>
       </c>
       <c r="G43">
         <v>0.006</v>
@@ -4807,28 +4807,28 @@
         <v>1.816530612244898</v>
       </c>
       <c r="M43">
-        <v>0.5910596900000001</v>
+        <v>0.6054757800000001</v>
       </c>
       <c r="N43">
-        <v>1.225470922244898</v>
+        <v>1.211054832244898</v>
       </c>
       <c r="O43">
-        <v>0.1838206383367347</v>
+        <v>0.1816582248367347</v>
       </c>
       <c r="P43">
-        <v>1.041650283908163</v>
+        <v>1.029396607408163</v>
       </c>
       <c r="Q43">
-        <v>1.551650283908163</v>
+        <v>1.539396607408163</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.09605188601844561</v>
+        <v>0.09683659571873181</v>
       </c>
       <c r="T43">
-        <v>0.92038094016126</v>
+        <v>0.9347531739006657</v>
       </c>
       <c r="U43">
         <v>0.0641</v>
@@ -4845,7 +4845,7 @@
         </is>
       </c>
       <c r="Y43">
-        <v>3.07334545559163</v>
+        <v>3.000170563791829</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4853,22 +4853,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.07904892551686445</v>
+        <v>0.081939288282846</v>
       </c>
       <c r="C44">
-        <v>13.0558525410343</v>
+        <v>11.03178604964751</v>
       </c>
       <c r="D44">
-        <v>22.4956525410343</v>
+        <v>20.69648604964751</v>
       </c>
       <c r="E44">
-        <v>2.8558</v>
+        <v>3.0807</v>
       </c>
       <c r="F44">
-        <v>9.4458</v>
+        <v>9.6707</v>
       </c>
       <c r="G44">
         <v>0.006</v>
@@ -4889,45 +4889,45 @@
         <v>1.816530612244898</v>
       </c>
       <c r="M44">
-        <v>0.60547578</v>
+        <v>0.69532333</v>
       </c>
       <c r="N44">
-        <v>1.211054832244898</v>
+        <v>1.121207282244898</v>
       </c>
       <c r="O44">
-        <v>0.1816582248367347</v>
+        <v>0.1681810923367347</v>
       </c>
       <c r="P44">
-        <v>1.029396607408164</v>
+        <v>0.9530261899081635</v>
       </c>
       <c r="Q44">
-        <v>1.539396607408163</v>
+        <v>1.463026189908163</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.09683659571873179</v>
+        <v>0.09764883909271226</v>
       </c>
       <c r="T44">
-        <v>0.9347531739006656</v>
+        <v>0.9496296965432084</v>
       </c>
       <c r="U44">
-        <v>0.0641</v>
+        <v>0.07190000000000001</v>
       </c>
       <c r="V44">
         <v>0.15</v>
       </c>
       <c r="W44">
-        <v>0.054485</v>
+        <v>0.061115</v>
       </c>
       <c r="X44" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y44">
-        <v>3.00017056379183</v>
+        <v>2.612497717061929</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -4935,22 +4935,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.081939288282846</v>
+        <v>0.08204505104882753</v>
       </c>
       <c r="C45">
-        <v>11.03178604964751</v>
+        <v>10.74649387065016</v>
       </c>
       <c r="D45">
-        <v>20.69648604964751</v>
+        <v>20.63609387065016</v>
       </c>
       <c r="E45">
-        <v>3.0807</v>
+        <v>3.305600000000002</v>
       </c>
       <c r="F45">
-        <v>9.6707</v>
+        <v>9.895600000000002</v>
       </c>
       <c r="G45">
         <v>0.006</v>
@@ -4971,28 +4971,28 @@
         <v>1.816530612244898</v>
       </c>
       <c r="M45">
-        <v>0.69532333</v>
+        <v>0.7114936400000001</v>
       </c>
       <c r="N45">
-        <v>1.121207282244898</v>
+        <v>1.105036972244898</v>
       </c>
       <c r="O45">
-        <v>0.1681810923367347</v>
+        <v>0.1657555458367347</v>
       </c>
       <c r="P45">
-        <v>0.9530261899081635</v>
+        <v>0.9392814264081634</v>
       </c>
       <c r="Q45">
-        <v>1.463026189908163</v>
+        <v>1.449281426408163</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.09764883909271226</v>
+        <v>0.09849009115862059</v>
       </c>
       <c r="T45">
-        <v>0.9496296965432084</v>
+        <v>0.9650375235658419</v>
       </c>
       <c r="U45">
         <v>0.07190000000000001</v>
@@ -5009,7 +5009,7 @@
         </is>
       </c>
       <c r="Y45">
-        <v>2.612497717061929</v>
+        <v>2.553122768946885</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5017,22 +5017,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.08204505104882753</v>
+        <v>0.08364256381480907</v>
       </c>
       <c r="C46">
-        <v>10.74649387065016</v>
+        <v>9.650447202055359</v>
       </c>
       <c r="D46">
-        <v>20.63609387065016</v>
+        <v>19.76494720205536</v>
       </c>
       <c r="E46">
-        <v>3.305600000000002</v>
+        <v>3.530500000000002</v>
       </c>
       <c r="F46">
-        <v>9.895600000000002</v>
+        <v>10.1205</v>
       </c>
       <c r="G46">
         <v>0.006</v>
@@ -5053,45 +5053,45 @@
         <v>1.816530612244898</v>
       </c>
       <c r="M46">
-        <v>0.7114936400000001</v>
+        <v>0.7671339000000001</v>
       </c>
       <c r="N46">
-        <v>1.105036972244898</v>
+        <v>1.049396712244898</v>
       </c>
       <c r="O46">
-        <v>0.1657555458367347</v>
+        <v>0.1574095068367347</v>
       </c>
       <c r="P46">
-        <v>0.9392814264081634</v>
+        <v>0.8919872054081632</v>
       </c>
       <c r="Q46">
-        <v>1.449281426408163</v>
+        <v>1.401987205408163</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.09849009115862059</v>
+        <v>0.09936193420874376</v>
       </c>
       <c r="T46">
-        <v>0.9650375235658419</v>
+        <v>0.9810056352074803</v>
       </c>
       <c r="U46">
-        <v>0.07190000000000001</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V46">
         <v>0.15</v>
       </c>
       <c r="W46">
-        <v>0.061115</v>
+        <v>0.06443</v>
       </c>
       <c r="X46" t="inlineStr">
         <is>
-          <t>B1/B+</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y46">
-        <v>2.553122768946885</v>
+        <v>2.367944647270702</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5099,22 +5099,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.08364256381480907</v>
+        <v>0.08378147658079062</v>
       </c>
       <c r="C47">
-        <v>9.650447202055359</v>
+        <v>9.353259241383881</v>
       </c>
       <c r="D47">
-        <v>19.76494720205536</v>
+        <v>19.69265924138388</v>
       </c>
       <c r="E47">
-        <v>3.530500000000002</v>
+        <v>3.755400000000002</v>
       </c>
       <c r="F47">
-        <v>10.1205</v>
+        <v>10.3454</v>
       </c>
       <c r="G47">
         <v>0.006</v>
@@ -5135,28 +5135,28 @@
         <v>1.816530612244898</v>
       </c>
       <c r="M47">
-        <v>0.7671339000000001</v>
+        <v>0.7841813200000002</v>
       </c>
       <c r="N47">
-        <v>1.049396712244898</v>
+        <v>1.032349292244898</v>
       </c>
       <c r="O47">
-        <v>0.1574095068367347</v>
+        <v>0.1548523938367347</v>
       </c>
       <c r="P47">
-        <v>0.8919872054081632</v>
+        <v>0.8774968984081634</v>
       </c>
       <c r="Q47">
-        <v>1.401987205408163</v>
+        <v>1.387496898408163</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.09936193420874376</v>
+        <v>0.1002660677422048</v>
       </c>
       <c r="T47">
-        <v>0.9810056352074803</v>
+        <v>0.9975651583914017</v>
       </c>
       <c r="U47">
         <v>0.07580000000000001</v>
@@ -5173,7 +5173,7 @@
         </is>
       </c>
       <c r="Y47">
-        <v>2.367944647270702</v>
+        <v>2.316467589721339</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5181,22 +5181,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.08378147658079062</v>
+        <v>0.08392038934677216</v>
       </c>
       <c r="C48">
-        <v>9.353259241383881</v>
+        <v>9.056598123209879</v>
       </c>
       <c r="D48">
-        <v>19.69265924138388</v>
+        <v>19.62089812320988</v>
       </c>
       <c r="E48">
-        <v>3.755400000000002</v>
+        <v>3.980300000000002</v>
       </c>
       <c r="F48">
-        <v>10.3454</v>
+        <v>10.5703</v>
       </c>
       <c r="G48">
         <v>0.006</v>
@@ -5217,28 +5217,28 @@
         <v>1.816530612244898</v>
       </c>
       <c r="M48">
-        <v>0.7841813200000002</v>
+        <v>0.8012287400000002</v>
       </c>
       <c r="N48">
-        <v>1.032349292244898</v>
+        <v>1.015301872244898</v>
       </c>
       <c r="O48">
-        <v>0.1548523938367347</v>
+        <v>0.1522952808367347</v>
       </c>
       <c r="P48">
-        <v>0.8774968984081634</v>
+        <v>0.8630065914081632</v>
       </c>
       <c r="Q48">
-        <v>1.387496898408163</v>
+        <v>1.373006591408163</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.1002660677422048</v>
+        <v>0.1012043195222116</v>
       </c>
       <c r="T48">
-        <v>0.9975651583914017</v>
+        <v>1.014749569242641</v>
       </c>
       <c r="U48">
         <v>0.07580000000000001</v>
@@ -5255,7 +5255,7 @@
         </is>
       </c>
       <c r="Y48">
-        <v>2.316467589721339</v>
+        <v>2.267181045259182</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5263,22 +5263,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.08392038934677216</v>
+        <v>0.0840593021127537</v>
       </c>
       <c r="C49">
-        <v>9.056598123209879</v>
+        <v>8.760458108917295</v>
       </c>
       <c r="D49">
-        <v>19.62089812320988</v>
+        <v>19.5496581089173</v>
       </c>
       <c r="E49">
-        <v>3.980300000000002</v>
+        <v>4.205200000000001</v>
       </c>
       <c r="F49">
-        <v>10.5703</v>
+        <v>10.7952</v>
       </c>
       <c r="G49">
         <v>0.006</v>
@@ -5299,28 +5299,28 @@
         <v>1.816530612244898</v>
       </c>
       <c r="M49">
-        <v>0.8012287400000002</v>
+        <v>0.8182761600000001</v>
       </c>
       <c r="N49">
-        <v>1.015301872244898</v>
+        <v>0.9982544522448979</v>
       </c>
       <c r="O49">
-        <v>0.1522952808367347</v>
+        <v>0.1497381678367347</v>
       </c>
       <c r="P49">
-        <v>0.8630065914081632</v>
+        <v>0.8485162844081633</v>
       </c>
       <c r="Q49">
-        <v>1.373006591408163</v>
+        <v>1.358516284408163</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.1012043195222116</v>
+        <v>0.1021786579091417</v>
       </c>
       <c r="T49">
-        <v>1.014749569242641</v>
+        <v>1.032594918972774</v>
       </c>
       <c r="U49">
         <v>0.07580000000000001</v>
@@ -5337,7 +5337,7 @@
         </is>
       </c>
       <c r="Y49">
-        <v>2.267181045259182</v>
+        <v>2.219948106816283</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5345,22 +5345,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.0840593021127537</v>
+        <v>0.08419821487873522</v>
       </c>
       <c r="C50">
-        <v>8.760458108917295</v>
+        <v>8.464833542932153</v>
       </c>
       <c r="D50">
-        <v>19.5496581089173</v>
+        <v>19.47893354293215</v>
       </c>
       <c r="E50">
-        <v>4.205200000000001</v>
+        <v>4.430100000000001</v>
       </c>
       <c r="F50">
-        <v>10.7952</v>
+        <v>11.0201</v>
       </c>
       <c r="G50">
         <v>0.006</v>
@@ -5381,28 +5381,28 @@
         <v>1.816530612244898</v>
       </c>
       <c r="M50">
-        <v>0.8182761600000001</v>
+        <v>0.8353235800000002</v>
       </c>
       <c r="N50">
-        <v>0.9982544522448979</v>
+        <v>0.9812070322448979</v>
       </c>
       <c r="O50">
-        <v>0.1497381678367347</v>
+        <v>0.1471810548367347</v>
       </c>
       <c r="P50">
-        <v>0.8485162844081633</v>
+        <v>0.8340259774081632</v>
       </c>
       <c r="Q50">
-        <v>1.358516284408163</v>
+        <v>1.344025977408163</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.1021786579091417</v>
+        <v>0.1031912056445789</v>
       </c>
       <c r="T50">
-        <v>1.032594918972774</v>
+        <v>1.051140086339382</v>
       </c>
       <c r="U50">
         <v>0.07580000000000001</v>
@@ -5419,7 +5419,7 @@
         </is>
       </c>
       <c r="Y50">
-        <v>2.219948106816283</v>
+        <v>2.174643043411869</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5427,22 +5427,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.08419821487873522</v>
+        <v>0.08433712764471676</v>
       </c>
       <c r="C51">
-        <v>8.464833542932153</v>
+        <v>8.16971885122587</v>
       </c>
       <c r="D51">
-        <v>19.47893354293215</v>
+        <v>19.40871885122587</v>
       </c>
       <c r="E51">
-        <v>4.430100000000001</v>
+        <v>4.655000000000001</v>
       </c>
       <c r="F51">
-        <v>11.0201</v>
+        <v>11.245</v>
       </c>
       <c r="G51">
         <v>0.006</v>
@@ -5463,28 +5463,28 @@
         <v>1.816530612244898</v>
       </c>
       <c r="M51">
-        <v>0.8353235800000002</v>
+        <v>0.8523710000000001</v>
       </c>
       <c r="N51">
-        <v>0.9812070322448979</v>
+        <v>0.964159612244898</v>
       </c>
       <c r="O51">
-        <v>0.1471810548367347</v>
+        <v>0.1446239418367347</v>
       </c>
       <c r="P51">
-        <v>0.8340259774081632</v>
+        <v>0.8195356704081633</v>
       </c>
       <c r="Q51">
-        <v>1.344025977408163</v>
+        <v>1.329535670408163</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.1031912056445789</v>
+        <v>0.1042442552894335</v>
       </c>
       <c r="T51">
-        <v>1.051140086339382</v>
+        <v>1.070427060400656</v>
       </c>
       <c r="U51">
         <v>0.07580000000000001</v>
@@ -5501,7 +5501,7 @@
         </is>
       </c>
       <c r="Y51">
-        <v>2.174643043411869</v>
+        <v>2.131150182543632</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5509,22 +5509,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.08433712764471676</v>
+        <v>0.08447604041069831</v>
       </c>
       <c r="C52">
-        <v>8.16971885122587</v>
+        <v>7.875108539850869</v>
       </c>
       <c r="D52">
-        <v>19.40871885122587</v>
+        <v>19.33900853985087</v>
       </c>
       <c r="E52">
-        <v>4.655000000000001</v>
+        <v>4.879900000000001</v>
       </c>
       <c r="F52">
-        <v>11.245</v>
+        <v>11.4699</v>
       </c>
       <c r="G52">
         <v>0.006</v>
@@ -5545,28 +5545,28 @@
         <v>1.816530612244898</v>
       </c>
       <c r="M52">
-        <v>0.8523710000000001</v>
+        <v>0.8694184200000001</v>
       </c>
       <c r="N52">
-        <v>0.964159612244898</v>
+        <v>0.947112192244898</v>
       </c>
       <c r="O52">
-        <v>0.1446239418367347</v>
+        <v>0.1420668288367347</v>
       </c>
       <c r="P52">
-        <v>0.8195356704081633</v>
+        <v>0.8050453634081632</v>
       </c>
       <c r="Q52">
-        <v>1.329535670408163</v>
+        <v>1.315045363408163</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.1042442552894335</v>
+        <v>0.1053402865524455</v>
       </c>
       <c r="T52">
-        <v>1.070427060400656</v>
+        <v>1.090501257893001</v>
       </c>
       <c r="U52">
         <v>0.07580000000000001</v>
@@ -5583,7 +5583,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>2.131150182543632</v>
+        <v>2.089362924062384</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5591,22 +5591,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.08447604041069831</v>
+        <v>0.08461495317667984</v>
       </c>
       <c r="C53">
-        <v>7.875108539850869</v>
+        <v>7.580997193507542</v>
       </c>
       <c r="D53">
-        <v>19.33900853985087</v>
+        <v>19.26979719350754</v>
       </c>
       <c r="E53">
-        <v>4.879900000000001</v>
+        <v>5.104800000000001</v>
       </c>
       <c r="F53">
-        <v>11.4699</v>
+        <v>11.6948</v>
       </c>
       <c r="G53">
         <v>0.006</v>
@@ -5627,28 +5627,28 @@
         <v>1.816530612244898</v>
       </c>
       <c r="M53">
-        <v>0.8694184200000001</v>
+        <v>0.8864658400000002</v>
       </c>
       <c r="N53">
-        <v>0.947112192244898</v>
+        <v>0.9300647722448979</v>
       </c>
       <c r="O53">
-        <v>0.1420668288367347</v>
+        <v>0.1395097158367347</v>
       </c>
       <c r="P53">
-        <v>0.8050453634081632</v>
+        <v>0.7905550564081633</v>
       </c>
       <c r="Q53">
-        <v>1.315045363408163</v>
+        <v>1.300555056408163</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.1053402865524455</v>
+        <v>0.1064819857847497</v>
       </c>
       <c r="T53">
-        <v>1.090501257893001</v>
+        <v>1.111411880280861</v>
       </c>
       <c r="U53">
         <v>0.07580000000000001</v>
@@ -5665,7 +5665,7 @@
         </is>
       </c>
       <c r="Y53">
-        <v>2.089362924062384</v>
+        <v>2.049182867830415</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5673,22 +5673,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.08461495317667984</v>
+        <v>0.08475386594266139</v>
       </c>
       <c r="C54">
-        <v>7.580997193507542</v>
+        <v>7.287379474141925</v>
       </c>
       <c r="D54">
-        <v>19.26979719350754</v>
+        <v>19.20107947414193</v>
       </c>
       <c r="E54">
-        <v>5.104800000000001</v>
+        <v>5.329700000000003</v>
       </c>
       <c r="F54">
-        <v>11.6948</v>
+        <v>11.9197</v>
       </c>
       <c r="G54">
         <v>0.006</v>
@@ -5709,28 +5709,28 @@
         <v>1.816530612244898</v>
       </c>
       <c r="M54">
-        <v>0.8864658400000002</v>
+        <v>0.9035132600000002</v>
       </c>
       <c r="N54">
-        <v>0.9300647722448979</v>
+        <v>0.9130173522448979</v>
       </c>
       <c r="O54">
-        <v>0.1395097158367347</v>
+        <v>0.1369526028367347</v>
       </c>
       <c r="P54">
-        <v>0.7905550564081633</v>
+        <v>0.7760647494081632</v>
       </c>
       <c r="Q54">
-        <v>1.300555056408163</v>
+        <v>1.286064749408163</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.1064819857847497</v>
+        <v>0.1076722679631093</v>
       </c>
       <c r="T54">
-        <v>1.111411880280861</v>
+        <v>1.133212316387353</v>
       </c>
       <c r="U54">
         <v>0.07580000000000001</v>
@@ -5747,7 +5747,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>2.049182867830415</v>
+        <v>2.010519040135502</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5755,22 +5755,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.08475386594266139</v>
+        <v>0.09141057870864293</v>
       </c>
       <c r="C55">
-        <v>7.287379474141925</v>
+        <v>4.260145575407018</v>
       </c>
       <c r="D55">
-        <v>19.20107947414193</v>
+        <v>16.39874557540702</v>
       </c>
       <c r="E55">
-        <v>5.329700000000003</v>
+        <v>5.554600000000002</v>
       </c>
       <c r="F55">
-        <v>11.9197</v>
+        <v>12.1446</v>
       </c>
       <c r="G55">
         <v>0.006</v>
@@ -5791,45 +5791,45 @@
         <v>1.816530612244898</v>
       </c>
       <c r="M55">
-        <v>0.9035132600000002</v>
+        <v>1.093014</v>
       </c>
       <c r="N55">
-        <v>0.9130173522448979</v>
+        <v>0.7235166122448979</v>
       </c>
       <c r="O55">
-        <v>0.1369526028367347</v>
+        <v>0.1085274918367347</v>
       </c>
       <c r="P55">
-        <v>0.7760647494081632</v>
+        <v>0.6149891204081632</v>
       </c>
       <c r="Q55">
-        <v>1.286064749408163</v>
+        <v>1.124989120408163</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.1076722679631093</v>
+        <v>0.1089143015405281</v>
       </c>
       <c r="T55">
-        <v>1.133212316387353</v>
+        <v>1.155960597541954</v>
       </c>
       <c r="U55">
-        <v>0.07580000000000001</v>
+        <v>0.09</v>
       </c>
       <c r="V55">
         <v>0.15</v>
       </c>
       <c r="W55">
-        <v>0.06443</v>
+        <v>0.0765</v>
       </c>
       <c r="X55" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y55">
-        <v>2.010519040135502</v>
+        <v>1.661946335769622</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5837,22 +5837,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.09141057870864293</v>
+        <v>0.09167019147462446</v>
       </c>
       <c r="C56">
-        <v>4.260145575407018</v>
+        <v>3.94243315059266</v>
       </c>
       <c r="D56">
-        <v>16.39874557540702</v>
+        <v>16.30593315059266</v>
       </c>
       <c r="E56">
-        <v>5.554600000000002</v>
+        <v>5.779500000000002</v>
       </c>
       <c r="F56">
-        <v>12.1446</v>
+        <v>12.3695</v>
       </c>
       <c r="G56">
         <v>0.006</v>
@@ -5873,28 +5873,28 @@
         <v>1.816530612244898</v>
       </c>
       <c r="M56">
-        <v>1.093014</v>
+        <v>1.113255</v>
       </c>
       <c r="N56">
-        <v>0.7235166122448979</v>
+        <v>0.703275612244898</v>
       </c>
       <c r="O56">
-        <v>0.1085274918367347</v>
+        <v>0.1054913418367347</v>
       </c>
       <c r="P56">
-        <v>0.6149891204081632</v>
+        <v>0.5977842704081633</v>
       </c>
       <c r="Q56">
-        <v>1.124989120408163</v>
+        <v>1.107784270408163</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.1089143015405281</v>
+        <v>0.1102115366102766</v>
       </c>
       <c r="T56">
-        <v>1.155960597541954</v>
+        <v>1.179719913414536</v>
       </c>
       <c r="U56">
         <v>0.09</v>
@@ -5911,7 +5911,7 @@
         </is>
       </c>
       <c r="Y56">
-        <v>1.661946335769622</v>
+        <v>1.63172912966472</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -5919,22 +5919,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.09167019147462446</v>
+        <v>0.09192980424060601</v>
       </c>
       <c r="C57">
-        <v>3.94243315059266</v>
+        <v>3.62576539920452</v>
       </c>
       <c r="D57">
-        <v>16.30593315059266</v>
+        <v>16.21416539920452</v>
       </c>
       <c r="E57">
-        <v>5.779500000000002</v>
+        <v>6.004400000000002</v>
       </c>
       <c r="F57">
-        <v>12.3695</v>
+        <v>12.5944</v>
       </c>
       <c r="G57">
         <v>0.006</v>
@@ -5955,28 +5955,28 @@
         <v>1.816530612244898</v>
       </c>
       <c r="M57">
-        <v>1.113255</v>
+        <v>1.133496</v>
       </c>
       <c r="N57">
-        <v>0.703275612244898</v>
+        <v>0.683034612244898</v>
       </c>
       <c r="O57">
-        <v>0.1054913418367347</v>
+        <v>0.1024551918367347</v>
       </c>
       <c r="P57">
-        <v>0.5977842704081633</v>
+        <v>0.5805794204081633</v>
       </c>
       <c r="Q57">
-        <v>1.107784270408163</v>
+        <v>1.090579420408163</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.1102115366102766</v>
+        <v>0.1115677369104682</v>
       </c>
       <c r="T57">
-        <v>1.179719913414536</v>
+        <v>1.204559198190418</v>
       </c>
       <c r="U57">
         <v>0.09</v>
@@ -5993,7 +5993,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>1.63172912966472</v>
+        <v>1.602591109492136</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -6001,22 +6001,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.09192980424060601</v>
+        <v>0.09218941700658756</v>
       </c>
       <c r="C58">
-        <v>3.62576539920452</v>
+        <v>3.310124782076866</v>
       </c>
       <c r="D58">
-        <v>16.21416539920452</v>
+        <v>16.12342478207687</v>
       </c>
       <c r="E58">
-        <v>6.004400000000002</v>
+        <v>6.229300000000002</v>
       </c>
       <c r="F58">
-        <v>12.5944</v>
+        <v>12.8193</v>
       </c>
       <c r="G58">
         <v>0.006</v>
@@ -6037,28 +6037,28 @@
         <v>1.816530612244898</v>
       </c>
       <c r="M58">
-        <v>1.133496</v>
+        <v>1.153737</v>
       </c>
       <c r="N58">
-        <v>0.683034612244898</v>
+        <v>0.6627936122448979</v>
       </c>
       <c r="O58">
-        <v>0.1024551918367347</v>
+        <v>0.09941904183673468</v>
       </c>
       <c r="P58">
-        <v>0.5805794204081633</v>
+        <v>0.5633745704081632</v>
       </c>
       <c r="Q58">
-        <v>1.090579420408163</v>
+        <v>1.073374570408163</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.1115677369104682</v>
+        <v>0.1129870162943897</v>
       </c>
       <c r="T58">
-        <v>1.204559198190418</v>
+        <v>1.230553798537272</v>
       </c>
       <c r="U58">
         <v>0.09</v>
@@ -6075,7 +6075,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>1.602591109492136</v>
+        <v>1.574475475992274</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6083,22 +6083,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.09218941700658756</v>
+        <v>0.09244902977256909</v>
       </c>
       <c r="C59">
-        <v>3.310124782076866</v>
+        <v>2.995494150482216</v>
       </c>
       <c r="D59">
-        <v>16.12342478207687</v>
+        <v>16.03369415048222</v>
       </c>
       <c r="E59">
-        <v>6.229300000000002</v>
+        <v>6.454200000000004</v>
       </c>
       <c r="F59">
-        <v>12.8193</v>
+        <v>13.0442</v>
       </c>
       <c r="G59">
         <v>0.006</v>
@@ -6119,28 +6119,28 @@
         <v>1.816530612244898</v>
       </c>
       <c r="M59">
-        <v>1.153737</v>
+        <v>1.173978</v>
       </c>
       <c r="N59">
-        <v>0.6627936122448979</v>
+        <v>0.6425526122448979</v>
       </c>
       <c r="O59">
-        <v>0.09941904183673468</v>
+        <v>0.09638289183673468</v>
       </c>
       <c r="P59">
-        <v>0.5633745704081632</v>
+        <v>0.5461697204081633</v>
       </c>
       <c r="Q59">
-        <v>1.073374570408163</v>
+        <v>1.056169720408163</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.1129870162943897</v>
+        <v>0.1144738804108788</v>
       </c>
       <c r="T59">
-        <v>1.230553798537272</v>
+        <v>1.25778623699588</v>
       </c>
       <c r="U59">
         <v>0.09</v>
@@ -6157,7 +6157,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>1.574475475992274</v>
+        <v>1.547329347095855</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6165,22 +6165,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.09244902977256909</v>
+        <v>0.09270864253855063</v>
       </c>
       <c r="C60">
-        <v>2.995494150482219</v>
+        <v>2.681856735327052</v>
       </c>
       <c r="D60">
-        <v>16.03369415048222</v>
+        <v>15.94495673532705</v>
       </c>
       <c r="E60">
-        <v>6.4542</v>
+        <v>6.6791</v>
       </c>
       <c r="F60">
-        <v>13.0442</v>
+        <v>13.2691</v>
       </c>
       <c r="G60">
         <v>0.006</v>
@@ -6201,28 +6201,28 @@
         <v>1.816530612244898</v>
       </c>
       <c r="M60">
-        <v>1.173978</v>
+        <v>1.194219</v>
       </c>
       <c r="N60">
-        <v>0.6425526122448981</v>
+        <v>0.6223116122448982</v>
       </c>
       <c r="O60">
-        <v>0.09638289183673472</v>
+        <v>0.09334674183673472</v>
       </c>
       <c r="P60">
-        <v>0.5461697204081634</v>
+        <v>0.5289648704081634</v>
       </c>
       <c r="Q60">
-        <v>1.056169720408163</v>
+        <v>1.038964870408163</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.1144738804108788</v>
+        <v>0.1160332744842698</v>
       </c>
       <c r="T60">
-        <v>1.25778623699588</v>
+        <v>1.286347087086615</v>
       </c>
       <c r="U60">
         <v>0.09</v>
@@ -6239,7 +6239,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>1.547329347095856</v>
+        <v>1.521103425958638</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6247,22 +6247,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.09270864253855063</v>
+        <v>0.1232686151756947</v>
       </c>
       <c r="C61">
-        <v>2.681856735327052</v>
+        <v>-3.833041355214791</v>
       </c>
       <c r="D61">
-        <v>15.94495673532705</v>
+        <v>9.654958644785211</v>
       </c>
       <c r="E61">
-        <v>6.6791</v>
+        <v>6.904000000000002</v>
       </c>
       <c r="F61">
-        <v>13.2691</v>
+        <v>13.494</v>
       </c>
       <c r="G61">
         <v>0.006</v>
@@ -6283,45 +6283,45 @@
         <v>1.816530612244898</v>
       </c>
       <c r="M61">
-        <v>1.194219</v>
+        <v>1.9809192</v>
       </c>
       <c r="N61">
-        <v>0.6223116122448982</v>
+        <v>-0.1643885877551023</v>
       </c>
       <c r="O61">
-        <v>0.09334674183673472</v>
+        <v>-0.02465828816326535</v>
       </c>
       <c r="P61">
-        <v>0.5289648704081634</v>
+        <v>-0.139730299591837</v>
       </c>
       <c r="Q61">
-        <v>1.038964870408163</v>
+        <v>0.3702697004081628</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.1160332744842698</v>
+        <v>0.118260509908638</v>
       </c>
       <c r="T61">
-        <v>1.286347087086615</v>
+        <v>1.327139686056692</v>
       </c>
       <c r="U61">
-        <v>0.09</v>
+        <v>0.1468</v>
       </c>
       <c r="V61">
-        <v>0.15</v>
+        <v>0.1375520979536847</v>
       </c>
       <c r="W61">
-        <v>0.0765</v>
+        <v>0.1266073520203991</v>
       </c>
       <c r="X61" t="inlineStr">
         <is>
-          <t>B3/B-</t>
+          <t>Ca2/CC</t>
         </is>
       </c>
       <c r="Y61">
-        <v>1.521103425958638</v>
+        <v>0.9170139863578978</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6329,22 +6329,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.1232686151756947</v>
+        <v>0.1242786151756947</v>
       </c>
       <c r="C62">
-        <v>-3.833041355214791</v>
+        <v>-4.182198239837465</v>
       </c>
       <c r="D62">
-        <v>9.654958644785211</v>
+        <v>9.530701760162536</v>
       </c>
       <c r="E62">
-        <v>6.904000000000002</v>
+        <v>7.128900000000002</v>
       </c>
       <c r="F62">
-        <v>13.494</v>
+        <v>13.7189</v>
       </c>
       <c r="G62">
         <v>0.006</v>
@@ -6365,37 +6365,37 @@
         <v>1.816530612244898</v>
       </c>
       <c r="M62">
-        <v>1.9809192</v>
+        <v>2.01393452</v>
       </c>
       <c r="N62">
-        <v>-0.1643885877551023</v>
+        <v>-0.1974039077551022</v>
       </c>
       <c r="O62">
-        <v>-0.02465828816326535</v>
+        <v>-0.02961058616326533</v>
       </c>
       <c r="P62">
-        <v>-0.139730299591837</v>
+        <v>-0.1677933215918369</v>
       </c>
       <c r="Q62">
-        <v>0.3702697004081628</v>
+        <v>0.3422066784081629</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.118260509908638</v>
+        <v>0.1201184717011672</v>
       </c>
       <c r="T62">
-        <v>1.327139686056692</v>
+        <v>1.361168908776095</v>
       </c>
       <c r="U62">
         <v>0.1468</v>
       </c>
       <c r="V62">
-        <v>0.1375520979536847</v>
+        <v>0.1352971455282144</v>
       </c>
       <c r="W62">
-        <v>0.1266073520203991</v>
+        <v>0.1269383790364581</v>
       </c>
       <c r="X62" t="inlineStr">
         <is>
@@ -6403,7 +6403,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>0.9170139863578978</v>
+        <v>0.9019809701880962</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6411,22 +6411,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.1242786151756947</v>
+        <v>0.1252886151756947</v>
       </c>
       <c r="C63">
-        <v>-4.182198239837465</v>
+        <v>-4.528197453309577</v>
       </c>
       <c r="D63">
-        <v>9.530701760162536</v>
+        <v>9.409602546690424</v>
       </c>
       <c r="E63">
-        <v>7.128900000000002</v>
+        <v>7.353800000000001</v>
       </c>
       <c r="F63">
-        <v>13.7189</v>
+        <v>13.9438</v>
       </c>
       <c r="G63">
         <v>0.006</v>
@@ -6447,37 +6447,37 @@
         <v>1.816530612244898</v>
       </c>
       <c r="M63">
-        <v>2.01393452</v>
+        <v>2.04694984</v>
       </c>
       <c r="N63">
-        <v>-0.1974039077551022</v>
+        <v>-0.2304192277551023</v>
       </c>
       <c r="O63">
-        <v>-0.02961058616326533</v>
+        <v>-0.03456288416326534</v>
       </c>
       <c r="P63">
-        <v>-0.1677933215918369</v>
+        <v>-0.1958563435918369</v>
       </c>
       <c r="Q63">
-        <v>0.3422066784081629</v>
+        <v>0.3141436564081629</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.1201184717011672</v>
+        <v>0.1220742209564611</v>
       </c>
       <c r="T63">
-        <v>1.361168908776095</v>
+        <v>1.396989143217571</v>
       </c>
       <c r="U63">
         <v>0.1468</v>
       </c>
       <c r="V63">
-        <v>0.1352971455282144</v>
+        <v>0.1331149335035658</v>
       </c>
       <c r="W63">
-        <v>0.1269383790364581</v>
+        <v>0.1272587277616766</v>
       </c>
       <c r="X63" t="inlineStr">
         <is>
@@ -6485,7 +6485,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>0.9019809701880962</v>
+        <v>0.887432890023772</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6493,22 +6493,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.1252886151756947</v>
+        <v>0.1262986151756947</v>
       </c>
       <c r="C64">
-        <v>-4.528197453309577</v>
+        <v>-4.871157851633383</v>
       </c>
       <c r="D64">
-        <v>9.409602546690424</v>
+        <v>9.291542148366618</v>
       </c>
       <c r="E64">
-        <v>7.353800000000001</v>
+        <v>7.578700000000001</v>
       </c>
       <c r="F64">
-        <v>13.9438</v>
+        <v>14.1687</v>
       </c>
       <c r="G64">
         <v>0.006</v>
@@ -6529,37 +6529,37 @@
         <v>1.816530612244898</v>
       </c>
       <c r="M64">
-        <v>2.04694984</v>
+        <v>2.07996516</v>
       </c>
       <c r="N64">
-        <v>-0.2304192277551023</v>
+        <v>-0.2634345477551023</v>
       </c>
       <c r="O64">
-        <v>-0.03456288416326534</v>
+        <v>-0.03951518216326535</v>
       </c>
       <c r="P64">
-        <v>-0.1958563435918369</v>
+        <v>-0.223919365591837</v>
       </c>
       <c r="Q64">
-        <v>0.3141436564081629</v>
+        <v>0.2860806344081628</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.1220742209564611</v>
+        <v>0.1241356863877168</v>
       </c>
       <c r="T64">
-        <v>1.396989143217571</v>
+        <v>1.434745606547775</v>
       </c>
       <c r="U64">
         <v>0.1468</v>
       </c>
       <c r="V64">
-        <v>0.1331149335035658</v>
+        <v>0.1310019980511282</v>
       </c>
       <c r="W64">
-        <v>0.1272587277616766</v>
+        <v>0.1275689066860944</v>
       </c>
       <c r="X64" t="inlineStr">
         <is>
@@ -6567,7 +6567,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>0.887432890023772</v>
+        <v>0.8733466536741883</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6575,22 +6575,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.1262986151756947</v>
+        <v>0.1273086151756947</v>
       </c>
       <c r="C65">
-        <v>-4.871157851633383</v>
+        <v>-5.211192399676209</v>
       </c>
       <c r="D65">
-        <v>9.291542148366618</v>
+        <v>9.176407600323792</v>
       </c>
       <c r="E65">
-        <v>7.578700000000001</v>
+        <v>7.803600000000001</v>
       </c>
       <c r="F65">
-        <v>14.1687</v>
+        <v>14.3936</v>
       </c>
       <c r="G65">
         <v>0.006</v>
@@ -6611,37 +6611,37 @@
         <v>1.816530612244898</v>
       </c>
       <c r="M65">
-        <v>2.07996516</v>
+        <v>2.11298048</v>
       </c>
       <c r="N65">
-        <v>-0.2634345477551023</v>
+        <v>-0.2964498677551024</v>
       </c>
       <c r="O65">
-        <v>-0.03951518216326535</v>
+        <v>-0.04446748016326536</v>
       </c>
       <c r="P65">
-        <v>-0.223919365591837</v>
+        <v>-0.2519823875918371</v>
       </c>
       <c r="Q65">
-        <v>0.2860806344081628</v>
+        <v>0.2580176124081627</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.1241356863877168</v>
+        <v>0.1263116776762645</v>
       </c>
       <c r="T65">
-        <v>1.434745606547775</v>
+        <v>1.474599651174102</v>
       </c>
       <c r="U65">
         <v>0.1468</v>
       </c>
       <c r="V65">
-        <v>0.1310019980511282</v>
+        <v>0.1289550918315794</v>
       </c>
       <c r="W65">
-        <v>0.1275689066860944</v>
+        <v>0.1278693925191242</v>
       </c>
       <c r="X65" t="inlineStr">
         <is>
@@ -6649,7 +6649,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>0.8733466536741883</v>
+        <v>0.8597006122105291</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6657,22 +6657,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.1273086151756947</v>
+        <v>0.1283186151756947</v>
       </c>
       <c r="C66">
-        <v>-5.211192399676209</v>
+        <v>-5.548408531697982</v>
       </c>
       <c r="D66">
-        <v>9.176407600323792</v>
+        <v>9.064091468302019</v>
       </c>
       <c r="E66">
-        <v>7.803600000000001</v>
+        <v>8.028500000000001</v>
       </c>
       <c r="F66">
-        <v>14.3936</v>
+        <v>14.6185</v>
       </c>
       <c r="G66">
         <v>0.006</v>
@@ -6693,37 +6693,37 @@
         <v>1.816530612244898</v>
       </c>
       <c r="M66">
-        <v>2.11298048</v>
+        <v>2.1459958</v>
       </c>
       <c r="N66">
-        <v>-0.2964498677551024</v>
+        <v>-0.329465187755102</v>
       </c>
       <c r="O66">
-        <v>-0.04446748016326536</v>
+        <v>-0.0494197781632653</v>
       </c>
       <c r="P66">
-        <v>-0.2519823875918371</v>
+        <v>-0.2800454095918367</v>
       </c>
       <c r="Q66">
-        <v>0.2580176124081627</v>
+        <v>0.2299545904081631</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.1263116776762645</v>
+        <v>0.1286120113241578</v>
       </c>
       <c r="T66">
-        <v>1.474599651174102</v>
+        <v>1.516731069779077</v>
       </c>
       <c r="U66">
         <v>0.1468</v>
       </c>
       <c r="V66">
-        <v>0.1289550918315794</v>
+        <v>0.1269711673418628</v>
       </c>
       <c r="W66">
-        <v>0.1278693925191242</v>
+        <v>0.1281606326342146</v>
       </c>
       <c r="X66" t="inlineStr">
         <is>
@@ -6731,7 +6731,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>0.8597006122105291</v>
+        <v>0.8464744489457519</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6739,22 +6739,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.1283186151756947</v>
+        <v>0.1293286151756947</v>
       </c>
       <c r="C67">
-        <v>-5.548408531697982</v>
+        <v>-5.882908485722464</v>
       </c>
       <c r="D67">
-        <v>9.064091468302019</v>
+        <v>8.954491514277539</v>
       </c>
       <c r="E67">
-        <v>8.028500000000001</v>
+        <v>8.253400000000003</v>
       </c>
       <c r="F67">
-        <v>14.6185</v>
+        <v>14.8434</v>
       </c>
       <c r="G67">
         <v>0.006</v>
@@ -6775,37 +6775,37 @@
         <v>1.816530612244898</v>
       </c>
       <c r="M67">
-        <v>2.1459958</v>
+        <v>2.179011120000001</v>
       </c>
       <c r="N67">
-        <v>-0.329465187755102</v>
+        <v>-0.3624805077551025</v>
       </c>
       <c r="O67">
-        <v>-0.0494197781632653</v>
+        <v>-0.05437207616326538</v>
       </c>
       <c r="P67">
-        <v>-0.2800454095918367</v>
+        <v>-0.3081084315918372</v>
       </c>
       <c r="Q67">
-        <v>0.2299545904081631</v>
+        <v>0.2018915684081626</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.1286120113241578</v>
+        <v>0.1310476587160448</v>
       </c>
       <c r="T67">
-        <v>1.516731069779077</v>
+        <v>1.56134080712552</v>
       </c>
       <c r="U67">
         <v>0.1468</v>
       </c>
       <c r="V67">
-        <v>0.1269711673418628</v>
+        <v>0.1250473617760769</v>
       </c>
       <c r="W67">
-        <v>0.1281606326342146</v>
+        <v>0.1284430472912719</v>
       </c>
       <c r="X67" t="inlineStr">
         <is>
@@ -6813,7 +6813,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>0.8464744489457519</v>
+        <v>0.8336490785071797</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6821,22 +6821,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.1293286151756947</v>
+        <v>0.1303386151756947</v>
       </c>
       <c r="C68">
-        <v>-5.882908485722464</v>
+        <v>-6.214789613939725</v>
       </c>
       <c r="D68">
-        <v>8.954491514277539</v>
+        <v>8.847510386060277</v>
       </c>
       <c r="E68">
-        <v>8.253400000000003</v>
+        <v>8.478300000000003</v>
       </c>
       <c r="F68">
-        <v>14.8434</v>
+        <v>15.0683</v>
       </c>
       <c r="G68">
         <v>0.006</v>
@@ -6857,37 +6857,37 @@
         <v>1.816530612244898</v>
       </c>
       <c r="M68">
-        <v>2.179011120000001</v>
+        <v>2.212026440000001</v>
       </c>
       <c r="N68">
-        <v>-0.3624805077551025</v>
+        <v>-0.3954958277551026</v>
       </c>
       <c r="O68">
-        <v>-0.05437207616326538</v>
+        <v>-0.05932437416326539</v>
       </c>
       <c r="P68">
-        <v>-0.3081084315918372</v>
+        <v>-0.3361714535918372</v>
       </c>
       <c r="Q68">
-        <v>0.2018915684081626</v>
+        <v>0.1738285464081626</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.1310476587160448</v>
+        <v>0.1336309211013795</v>
       </c>
       <c r="T68">
-        <v>1.56134080712552</v>
+        <v>1.608654164917203</v>
       </c>
       <c r="U68">
         <v>0.1468</v>
       </c>
       <c r="V68">
-        <v>0.1250473617760769</v>
+        <v>0.1231809832421056</v>
       </c>
       <c r="W68">
-        <v>0.1284430472912719</v>
+        <v>0.1287170316600589</v>
       </c>
       <c r="X68" t="inlineStr">
         <is>
@@ -6895,7 +6895,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>0.8336490785071797</v>
+        <v>0.821206554947371</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -6903,22 +6903,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.1303386151756947</v>
+        <v>0.1313486151756947</v>
       </c>
       <c r="C69">
-        <v>-6.214789613939725</v>
+        <v>-6.544144671120588</v>
       </c>
       <c r="D69">
-        <v>8.847510386060277</v>
+        <v>8.743055328879414</v>
       </c>
       <c r="E69">
-        <v>8.478300000000003</v>
+        <v>8.703200000000002</v>
       </c>
       <c r="F69">
-        <v>15.0683</v>
+        <v>15.2932</v>
       </c>
       <c r="G69">
         <v>0.006</v>
@@ -6939,37 +6939,37 @@
         <v>1.816530612244898</v>
       </c>
       <c r="M69">
-        <v>2.212026440000001</v>
+        <v>2.245041760000001</v>
       </c>
       <c r="N69">
-        <v>-0.3954958277551026</v>
+        <v>-0.4285111477551027</v>
       </c>
       <c r="O69">
-        <v>-0.05932437416326539</v>
+        <v>-0.06427667216326539</v>
       </c>
       <c r="P69">
-        <v>-0.3361714535918372</v>
+        <v>-0.3642344755918373</v>
       </c>
       <c r="Q69">
-        <v>0.1738285464081626</v>
+        <v>0.1457655244081625</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.1336309211013795</v>
+        <v>0.1363756373857976</v>
       </c>
       <c r="T69">
-        <v>1.608654164917203</v>
+        <v>1.658924607570865</v>
       </c>
       <c r="U69">
         <v>0.1468</v>
       </c>
       <c r="V69">
-        <v>0.1231809832421056</v>
+        <v>0.1213694981944276</v>
       </c>
       <c r="W69">
-        <v>0.1287170316600589</v>
+        <v>0.128982957665058</v>
       </c>
       <c r="X69" t="inlineStr">
         <is>
@@ -6977,7 +6977,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>0.821206554947371</v>
+        <v>0.8091299879628508</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -6985,22 +6985,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.1313486151756947</v>
+        <v>0.1703197775792702</v>
       </c>
       <c r="C70">
-        <v>-6.544144671120588</v>
+        <v>-9.505373274890351</v>
       </c>
       <c r="D70">
-        <v>8.743055328879414</v>
+        <v>6.006726725109651</v>
       </c>
       <c r="E70">
-        <v>8.703200000000002</v>
+        <v>8.928100000000002</v>
       </c>
       <c r="F70">
-        <v>15.2932</v>
+        <v>15.5181</v>
       </c>
       <c r="G70">
         <v>0.006</v>
@@ -7021,45 +7021,45 @@
         <v>1.816530612244898</v>
       </c>
       <c r="M70">
-        <v>2.245041760000001</v>
+        <v>3.116034480000001</v>
       </c>
       <c r="N70">
-        <v>-0.4285111477551027</v>
+        <v>-1.299503867755103</v>
       </c>
       <c r="O70">
-        <v>-0.06427667216326539</v>
+        <v>-0.1949255801632654</v>
       </c>
       <c r="P70">
-        <v>-0.3642344755918373</v>
+        <v>-1.104578287591837</v>
       </c>
       <c r="Q70">
-        <v>0.1457655244081625</v>
+        <v>-0.5945782875918373</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.1363756373857976</v>
+        <v>0.1415592463452605</v>
       </c>
       <c r="T70">
-        <v>1.658924607570865</v>
+        <v>1.753864226071703</v>
       </c>
       <c r="U70">
-        <v>0.1468</v>
+        <v>0.2008</v>
       </c>
       <c r="V70">
-        <v>0.1213694981944276</v>
+        <v>0.08744434427334535</v>
       </c>
       <c r="W70">
-        <v>0.128982957665058</v>
+        <v>0.1832411756699123</v>
       </c>
       <c r="X70" t="inlineStr">
         <is>
-          <t>Ca2/CC</t>
+          <t>C2/C</t>
         </is>
       </c>
       <c r="Y70">
-        <v>0.8091299879628508</v>
+        <v>0.5829622951556357</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7067,22 +7067,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.1703197775792702</v>
+        <v>0.1718697775792702</v>
       </c>
       <c r="C71">
-        <v>-9.505373274890351</v>
+        <v>-9.80412464992007</v>
       </c>
       <c r="D71">
-        <v>6.006726725109651</v>
+        <v>5.932875350079931</v>
       </c>
       <c r="E71">
-        <v>8.928100000000002</v>
+        <v>9.153000000000002</v>
       </c>
       <c r="F71">
-        <v>15.5181</v>
+        <v>15.743</v>
       </c>
       <c r="G71">
         <v>0.006</v>
@@ -7103,37 +7103,37 @@
         <v>1.816530612244898</v>
       </c>
       <c r="M71">
-        <v>3.116034480000001</v>
+        <v>3.161194400000001</v>
       </c>
       <c r="N71">
-        <v>-1.299503867755103</v>
+        <v>-1.344663787755103</v>
       </c>
       <c r="O71">
-        <v>-0.1949255801632654</v>
+        <v>-0.2016995681632654</v>
       </c>
       <c r="P71">
-        <v>-1.104578287591837</v>
+        <v>-1.142964219591837</v>
       </c>
       <c r="Q71">
-        <v>-0.5945782875918373</v>
+        <v>-0.6329642195918375</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.1415592463452605</v>
+        <v>0.1447512212234358</v>
       </c>
       <c r="T71">
-        <v>1.753864226071703</v>
+        <v>1.812326366940759</v>
       </c>
       <c r="U71">
         <v>0.2008</v>
       </c>
       <c r="V71">
-        <v>0.08744434427334535</v>
+        <v>0.0861951393551547</v>
       </c>
       <c r="W71">
-        <v>0.1832411756699123</v>
+        <v>0.1834920160174849</v>
       </c>
       <c r="X71" t="inlineStr">
         <is>
@@ -7141,7 +7141,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>0.5829622951556357</v>
+        <v>0.574634262367698</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7149,22 +7149,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.1718697775792702</v>
+        <v>0.1734197775792702</v>
       </c>
       <c r="C72">
-        <v>-9.80412464992007</v>
+        <v>-10.10108210815308</v>
       </c>
       <c r="D72">
-        <v>5.932875350079931</v>
+        <v>5.860817891846925</v>
       </c>
       <c r="E72">
-        <v>9.153000000000002</v>
+        <v>9.377900000000004</v>
       </c>
       <c r="F72">
-        <v>15.743</v>
+        <v>15.9679</v>
       </c>
       <c r="G72">
         <v>0.006</v>
@@ -7185,37 +7185,37 @@
         <v>1.816530612244898</v>
       </c>
       <c r="M72">
-        <v>3.161194400000001</v>
+        <v>3.206354320000001</v>
       </c>
       <c r="N72">
-        <v>-1.344663787755103</v>
+        <v>-1.389823707755103</v>
       </c>
       <c r="O72">
-        <v>-0.2016995681632654</v>
+        <v>-0.2084735561632654</v>
       </c>
       <c r="P72">
-        <v>-1.142964219591837</v>
+        <v>-1.181350151591837</v>
       </c>
       <c r="Q72">
-        <v>-0.6329642195918375</v>
+        <v>-0.6713501515918376</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.1447512212234358</v>
+        <v>0.148163332300106</v>
       </c>
       <c r="T72">
-        <v>1.812326366940759</v>
+        <v>1.87482037959389</v>
       </c>
       <c r="U72">
         <v>0.2008</v>
       </c>
       <c r="V72">
-        <v>0.0861951393551547</v>
+        <v>0.08498112330789899</v>
       </c>
       <c r="W72">
-        <v>0.1834920160174849</v>
+        <v>0.1837357904397739</v>
       </c>
       <c r="X72" t="inlineStr">
         <is>
@@ -7223,7 +7223,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>0.574634262367698</v>
+        <v>0.56654082205266</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7231,22 +7231,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.1734197775792702</v>
+        <v>0.1749697775792702</v>
       </c>
       <c r="C73">
-        <v>-10.10108210815308</v>
+        <v>-10.39631022903869</v>
       </c>
       <c r="D73">
-        <v>5.860817891846925</v>
+        <v>5.790489770961313</v>
       </c>
       <c r="E73">
-        <v>9.3779</v>
+        <v>9.602800000000002</v>
       </c>
       <c r="F73">
-        <v>15.9679</v>
+        <v>16.1928</v>
       </c>
       <c r="G73">
         <v>0.006</v>
@@ -7267,37 +7267,37 @@
         <v>1.816530612244898</v>
       </c>
       <c r="M73">
-        <v>3.20635432</v>
+        <v>3.251514240000001</v>
       </c>
       <c r="N73">
-        <v>-1.389823707755102</v>
+        <v>-1.434983627755102</v>
       </c>
       <c r="O73">
-        <v>-0.2084735561632653</v>
+        <v>-0.2152475441632654</v>
       </c>
       <c r="P73">
-        <v>-1.181350151591837</v>
+        <v>-1.219736083591837</v>
       </c>
       <c r="Q73">
-        <v>-0.6713501515918368</v>
+        <v>-0.7097360835918374</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.148163332300106</v>
+        <v>0.1518191655965384</v>
       </c>
       <c r="T73">
-        <v>1.874820379593889</v>
+        <v>1.94177825029367</v>
       </c>
       <c r="U73">
         <v>0.2008</v>
       </c>
       <c r="V73">
-        <v>0.08498112330789902</v>
+        <v>0.08380082992862263</v>
       </c>
       <c r="W73">
-        <v>0.1837357904397739</v>
+        <v>0.1839727933503326</v>
       </c>
       <c r="X73" t="inlineStr">
         <is>
@@ -7305,7 +7305,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>0.5665408220526602</v>
+        <v>0.5586721995241508</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7313,22 +7313,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.1749697775792702</v>
+        <v>0.1765197775792702</v>
       </c>
       <c r="C74">
-        <v>-10.39631022903869</v>
+        <v>-10.68987052904224</v>
       </c>
       <c r="D74">
-        <v>5.790489770961313</v>
+        <v>5.721829470957761</v>
       </c>
       <c r="E74">
-        <v>9.602800000000002</v>
+        <v>9.8277</v>
       </c>
       <c r="F74">
-        <v>16.1928</v>
+        <v>16.4177</v>
       </c>
       <c r="G74">
         <v>0.006</v>
@@ -7349,37 +7349,37 @@
         <v>1.816530612244898</v>
       </c>
       <c r="M74">
-        <v>3.251514240000001</v>
+        <v>3.29667416</v>
       </c>
       <c r="N74">
-        <v>-1.434983627755102</v>
+        <v>-1.480143547755102</v>
       </c>
       <c r="O74">
-        <v>-0.2152475441632654</v>
+        <v>-0.2220215321632653</v>
       </c>
       <c r="P74">
-        <v>-1.219736083591837</v>
+        <v>-1.258122015591837</v>
       </c>
       <c r="Q74">
-        <v>-0.7097360835918374</v>
+        <v>-0.7481220155918371</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.1518191655965384</v>
+        <v>0.1557458013593731</v>
       </c>
       <c r="T74">
-        <v>1.94177825029367</v>
+        <v>2.01369596326751</v>
       </c>
       <c r="U74">
         <v>0.2008</v>
       </c>
       <c r="V74">
-        <v>0.08380082992862263</v>
+        <v>0.08265287335425794</v>
       </c>
       <c r="W74">
-        <v>0.1839727933503326</v>
+        <v>0.184203303030465</v>
       </c>
       <c r="X74" t="inlineStr">
         <is>
@@ -7387,7 +7387,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>0.5586721995241508</v>
+        <v>0.551019155695053</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7395,22 +7395,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.1765197775792702</v>
+        <v>0.1780697775792702</v>
       </c>
       <c r="C75">
-        <v>-10.68987052904224</v>
+        <v>-10.98182164111256</v>
       </c>
       <c r="D75">
-        <v>5.721829470957761</v>
+        <v>5.654778358887438</v>
       </c>
       <c r="E75">
-        <v>9.8277</v>
+        <v>10.0526</v>
       </c>
       <c r="F75">
-        <v>16.4177</v>
+        <v>16.6426</v>
       </c>
       <c r="G75">
         <v>0.006</v>
@@ -7431,37 +7431,37 @@
         <v>1.816530612244898</v>
       </c>
       <c r="M75">
-        <v>3.29667416</v>
+        <v>3.34183408</v>
       </c>
       <c r="N75">
-        <v>-1.480143547755102</v>
+        <v>-1.525303467755102</v>
       </c>
       <c r="O75">
-        <v>-0.2220215321632653</v>
+        <v>-0.2287955201632653</v>
       </c>
       <c r="P75">
-        <v>-1.258122015591837</v>
+        <v>-1.296507947591837</v>
       </c>
       <c r="Q75">
-        <v>-0.7481220155918371</v>
+        <v>-0.7865079475918373</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.1557458013593731</v>
+        <v>0.1599744860270413</v>
       </c>
       <c r="T75">
-        <v>2.01369596326751</v>
+        <v>2.091145808008568</v>
       </c>
       <c r="U75">
         <v>0.2008</v>
       </c>
       <c r="V75">
-        <v>0.08265287335425794</v>
+        <v>0.08153594263325445</v>
       </c>
       <c r="W75">
-        <v>0.184203303030465</v>
+        <v>0.1844275827192425</v>
       </c>
       <c r="X75" t="inlineStr">
         <is>
@@ -7469,7 +7469,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>0.551019155695053</v>
+        <v>0.5435729508883631</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7477,22 +7477,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.1780697775792702</v>
+        <v>0.1796197775792702</v>
       </c>
       <c r="C76">
-        <v>-10.98182164111256</v>
+        <v>-11.27221948167715</v>
       </c>
       <c r="D76">
-        <v>5.654778358887438</v>
+        <v>5.589280518322848</v>
       </c>
       <c r="E76">
-        <v>10.0526</v>
+        <v>10.2775</v>
       </c>
       <c r="F76">
-        <v>16.6426</v>
+        <v>16.8675</v>
       </c>
       <c r="G76">
         <v>0.006</v>
@@ -7513,37 +7513,37 @@
         <v>1.816530612244898</v>
       </c>
       <c r="M76">
-        <v>3.34183408</v>
+        <v>3.386994</v>
       </c>
       <c r="N76">
-        <v>-1.525303467755102</v>
+        <v>-1.570463387755102</v>
       </c>
       <c r="O76">
-        <v>-0.2287955201632653</v>
+        <v>-0.2355695081632653</v>
       </c>
       <c r="P76">
-        <v>-1.296507947591837</v>
+        <v>-1.334893879591837</v>
       </c>
       <c r="Q76">
-        <v>-0.7865079475918373</v>
+        <v>-0.824893879591837</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.1599744860270413</v>
+        <v>0.164541465468123</v>
       </c>
       <c r="T76">
-        <v>2.091145808008568</v>
+        <v>2.174791640328911</v>
       </c>
       <c r="U76">
         <v>0.2008</v>
       </c>
       <c r="V76">
-        <v>0.08153594263325445</v>
+        <v>0.08044879673147774</v>
       </c>
       <c r="W76">
-        <v>0.1844275827192425</v>
+        <v>0.1846458816163193</v>
       </c>
       <c r="X76" t="inlineStr">
         <is>
@@ -7551,7 +7551,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>0.5435729508883631</v>
+        <v>0.536325311543185</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7559,22 +7559,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.1796197775792702</v>
+        <v>0.1811697775792702</v>
       </c>
       <c r="C77">
-        <v>-11.27221948167715</v>
+        <v>-11.5611174061646</v>
       </c>
       <c r="D77">
-        <v>5.589280518322848</v>
+        <v>5.525282593835404</v>
       </c>
       <c r="E77">
-        <v>10.2775</v>
+        <v>10.5024</v>
       </c>
       <c r="F77">
-        <v>16.8675</v>
+        <v>17.0924</v>
       </c>
       <c r="G77">
         <v>0.006</v>
@@ -7595,37 +7595,37 @@
         <v>1.816530612244898</v>
       </c>
       <c r="M77">
-        <v>3.386994</v>
+        <v>3.43215392</v>
       </c>
       <c r="N77">
-        <v>-1.570463387755102</v>
+        <v>-1.615623307755102</v>
       </c>
       <c r="O77">
-        <v>-0.2355695081632653</v>
+        <v>-0.2423434961632653</v>
       </c>
       <c r="P77">
-        <v>-1.334893879591837</v>
+        <v>-1.373279811591837</v>
       </c>
       <c r="Q77">
-        <v>-0.824893879591837</v>
+        <v>-0.863279811591837</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.164541465468123</v>
+        <v>0.1694890265292947</v>
       </c>
       <c r="T77">
-        <v>2.174791640328911</v>
+        <v>2.265407958675949</v>
       </c>
       <c r="U77">
         <v>0.2008</v>
       </c>
       <c r="V77">
-        <v>0.08044879673147774</v>
+        <v>0.07939025993237933</v>
       </c>
       <c r="W77">
-        <v>0.1846458816163193</v>
+        <v>0.1848584358055782</v>
       </c>
       <c r="X77" t="inlineStr">
         <is>
@@ -7633,7 +7633,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>0.536325311543185</v>
+        <v>0.5292683995491956</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7641,22 +7641,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.1811697775792702</v>
+        <v>0.1827197775792702</v>
       </c>
       <c r="C78">
-        <v>-11.5611174061646</v>
+        <v>-11.84856635396351</v>
       </c>
       <c r="D78">
-        <v>5.525282593835404</v>
+        <v>5.462733646036489</v>
       </c>
       <c r="E78">
-        <v>10.5024</v>
+        <v>10.7273</v>
       </c>
       <c r="F78">
-        <v>17.0924</v>
+        <v>17.3173</v>
       </c>
       <c r="G78">
         <v>0.006</v>
@@ -7677,37 +7677,37 @@
         <v>1.816530612244898</v>
       </c>
       <c r="M78">
-        <v>3.43215392</v>
+        <v>3.477313840000001</v>
       </c>
       <c r="N78">
-        <v>-1.615623307755102</v>
+        <v>-1.660783227755103</v>
       </c>
       <c r="O78">
-        <v>-0.2423434961632653</v>
+        <v>-0.2491174841632654</v>
       </c>
       <c r="P78">
-        <v>-1.373279811591837</v>
+        <v>-1.411665743591837</v>
       </c>
       <c r="Q78">
-        <v>-0.863279811591837</v>
+        <v>-0.9016657435918374</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.1694890265292947</v>
+        <v>0.174866810291438</v>
       </c>
       <c r="T78">
-        <v>2.265407958675949</v>
+        <v>2.363903956879251</v>
       </c>
       <c r="U78">
         <v>0.2008</v>
       </c>
       <c r="V78">
-        <v>0.07939025993237933</v>
+        <v>0.07835921759559518</v>
       </c>
       <c r="W78">
-        <v>0.1848584358055782</v>
+        <v>0.1850654691068045</v>
       </c>
       <c r="X78" t="inlineStr">
         <is>
@@ -7715,7 +7715,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>0.5292683995491956</v>
+        <v>0.5223947839706345</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7723,22 +7723,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.1827197775792702</v>
+        <v>0.1842697775792702</v>
       </c>
       <c r="C79">
-        <v>-11.84856635396351</v>
+        <v>-12.1346149836456</v>
       </c>
       <c r="D79">
-        <v>5.462733646036489</v>
+        <v>5.401585016354397</v>
       </c>
       <c r="E79">
-        <v>10.7273</v>
+        <v>10.9522</v>
       </c>
       <c r="F79">
-        <v>17.3173</v>
+        <v>17.5422</v>
       </c>
       <c r="G79">
         <v>0.006</v>
@@ -7759,37 +7759,37 @@
         <v>1.816530612244898</v>
       </c>
       <c r="M79">
-        <v>3.477313840000001</v>
+        <v>3.52247376</v>
       </c>
       <c r="N79">
-        <v>-1.660783227755103</v>
+        <v>-1.705943147755102</v>
       </c>
       <c r="O79">
-        <v>-0.2491174841632654</v>
+        <v>-0.2558914721632654</v>
       </c>
       <c r="P79">
-        <v>-1.411665743591837</v>
+        <v>-1.450051675591837</v>
       </c>
       <c r="Q79">
-        <v>-0.9016657435918374</v>
+        <v>-0.9400516755918371</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.174866810291438</v>
+        <v>0.1807334834865034</v>
       </c>
       <c r="T79">
-        <v>2.363903956879251</v>
+        <v>2.471354136737399</v>
       </c>
       <c r="U79">
         <v>0.2008</v>
       </c>
       <c r="V79">
-        <v>0.07835921759559518</v>
+        <v>0.0773546122418055</v>
       </c>
       <c r="W79">
-        <v>0.1850654691068045</v>
+        <v>0.1852671938618455</v>
       </c>
       <c r="X79" t="inlineStr">
         <is>
@@ -7797,7 +7797,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>0.5223947839706345</v>
+        <v>0.5156974149453701</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7805,22 +7805,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.1842697775792702</v>
+        <v>0.1858197775792702</v>
       </c>
       <c r="C80">
-        <v>-12.1346149836456</v>
+        <v>-12.41930979920735</v>
       </c>
       <c r="D80">
-        <v>5.401585016354397</v>
+        <v>5.341790200792648</v>
       </c>
       <c r="E80">
-        <v>10.9522</v>
+        <v>11.1771</v>
       </c>
       <c r="F80">
-        <v>17.5422</v>
+        <v>17.7671</v>
       </c>
       <c r="G80">
         <v>0.006</v>
@@ -7841,37 +7841,37 @@
         <v>1.816530612244898</v>
       </c>
       <c r="M80">
-        <v>3.52247376</v>
+        <v>3.567633680000001</v>
       </c>
       <c r="N80">
-        <v>-1.705943147755102</v>
+        <v>-1.751103067755102</v>
       </c>
       <c r="O80">
-        <v>-0.2558914721632654</v>
+        <v>-0.2626654601632654</v>
       </c>
       <c r="P80">
-        <v>-1.450051675591837</v>
+        <v>-1.488437607591837</v>
       </c>
       <c r="Q80">
-        <v>-0.9400516755918371</v>
+        <v>-0.9784376075918373</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.1807334834865034</v>
+        <v>0.1871588874620511</v>
       </c>
       <c r="T80">
-        <v>2.471354136737399</v>
+        <v>2.589037667058228</v>
       </c>
       <c r="U80">
         <v>0.2008</v>
       </c>
       <c r="V80">
-        <v>0.0773546122418055</v>
+        <v>0.07637543993494721</v>
       </c>
       <c r="W80">
-        <v>0.1852671938618455</v>
+        <v>0.1854638116610626</v>
       </c>
       <c r="X80" t="inlineStr">
         <is>
@@ -7879,7 +7879,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>0.5156974149453701</v>
+        <v>0.5091695995663148</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -7887,22 +7887,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.1858197775792702</v>
+        <v>0.1873697775792702</v>
       </c>
       <c r="C81">
-        <v>-12.41930979920735</v>
+        <v>-12.7026952680186</v>
       </c>
       <c r="D81">
-        <v>5.341790200792648</v>
+        <v>5.283304731981396</v>
       </c>
       <c r="E81">
-        <v>11.1771</v>
+        <v>11.402</v>
       </c>
       <c r="F81">
-        <v>17.7671</v>
+        <v>17.992</v>
       </c>
       <c r="G81">
         <v>0.006</v>
@@ -7923,37 +7923,37 @@
         <v>1.816530612244898</v>
       </c>
       <c r="M81">
-        <v>3.567633680000001</v>
+        <v>3.6127936</v>
       </c>
       <c r="N81">
-        <v>-1.751103067755102</v>
+        <v>-1.796262987755102</v>
       </c>
       <c r="O81">
-        <v>-0.2626654601632654</v>
+        <v>-0.2694394481632653</v>
       </c>
       <c r="P81">
-        <v>-1.488437607591837</v>
+        <v>-1.526823539591837</v>
       </c>
       <c r="Q81">
-        <v>-0.9784376075918373</v>
+        <v>-1.016823539591837</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.1871588874620511</v>
+        <v>0.1942268318351537</v>
       </c>
       <c r="T81">
-        <v>2.589037667058228</v>
+        <v>2.718489550411139</v>
       </c>
       <c r="U81">
         <v>0.2008</v>
       </c>
       <c r="V81">
-        <v>0.07637543993494721</v>
+        <v>0.07542074693576038</v>
       </c>
       <c r="W81">
-        <v>0.1854638116610626</v>
+        <v>0.1856555140152993</v>
       </c>
       <c r="X81" t="inlineStr">
         <is>
@@ -7961,7 +7961,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>0.5091695995663148</v>
+        <v>0.5028049795717358</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -7969,22 +7969,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.1873697775792702</v>
+        <v>0.2175527050782156</v>
       </c>
       <c r="C82">
-        <v>-12.7026952680186</v>
+        <v>-13.8560557752788</v>
       </c>
       <c r="D82">
-        <v>5.283304731981396</v>
+        <v>4.354844224721206</v>
       </c>
       <c r="E82">
-        <v>11.402</v>
+        <v>11.6269</v>
       </c>
       <c r="F82">
-        <v>17.992</v>
+        <v>18.2169</v>
       </c>
       <c r="G82">
         <v>0.006</v>
@@ -8005,45 +8005,45 @@
         <v>1.816530612244898</v>
       </c>
       <c r="M82">
-        <v>3.6127936</v>
+        <v>4.29554502</v>
       </c>
       <c r="N82">
-        <v>-1.796262987755102</v>
+        <v>-2.479014407755102</v>
       </c>
       <c r="O82">
-        <v>-0.2694394481632653</v>
+        <v>-0.3718521611632654</v>
       </c>
       <c r="P82">
-        <v>-1.526823539591837</v>
+        <v>-2.107162246591837</v>
       </c>
       <c r="Q82">
-        <v>-1.016823539591837</v>
+        <v>-1.597162246591837</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.1942268318351537</v>
+        <v>0.2035278624525058</v>
       </c>
       <c r="T82">
-        <v>2.718489550411139</v>
+        <v>2.888841192554978</v>
       </c>
       <c r="U82">
-        <v>0.2008</v>
+        <v>0.2358</v>
       </c>
       <c r="V82">
-        <v>0.07542074693576038</v>
+        <v>0.06343306625074893</v>
       </c>
       <c r="W82">
-        <v>0.1856555140152993</v>
+        <v>0.2208424829780734</v>
       </c>
       <c r="X82" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>D2/D</t>
         </is>
       </c>
       <c r="Y82">
-        <v>0.5028049795717358</v>
+        <v>0.4228871083383263</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8051,22 +8051,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.2175527050782156</v>
+        <v>0.2194527050782156</v>
       </c>
       <c r="C83">
-        <v>-13.8560557752788</v>
+        <v>-14.12860377490681</v>
       </c>
       <c r="D83">
-        <v>4.354844224721206</v>
+        <v>4.307196225093193</v>
       </c>
       <c r="E83">
-        <v>11.6269</v>
+        <v>11.8518</v>
       </c>
       <c r="F83">
-        <v>18.2169</v>
+        <v>18.4418</v>
       </c>
       <c r="G83">
         <v>0.006</v>
@@ -8087,37 +8087,37 @@
         <v>1.816530612244898</v>
       </c>
       <c r="M83">
-        <v>4.29554502</v>
+        <v>4.348576440000001</v>
       </c>
       <c r="N83">
-        <v>-2.479014407755102</v>
+        <v>-2.532045827755103</v>
       </c>
       <c r="O83">
-        <v>-0.3718521611632654</v>
+        <v>-0.3798068741632655</v>
       </c>
       <c r="P83">
-        <v>-2.107162246591837</v>
+        <v>-2.152238953591838</v>
       </c>
       <c r="Q83">
-        <v>-1.597162246591837</v>
+        <v>-1.642238953591838</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.2035278624525058</v>
+        <v>0.212290521477645</v>
       </c>
       <c r="T83">
-        <v>2.888841192554978</v>
+        <v>3.049332369919143</v>
       </c>
       <c r="U83">
         <v>0.2358</v>
       </c>
       <c r="V83">
-        <v>0.06343306625074893</v>
+        <v>0.06265949227208126</v>
       </c>
       <c r="W83">
-        <v>0.2208424829780734</v>
+        <v>0.2210248917222433</v>
       </c>
       <c r="X83" t="inlineStr">
         <is>
@@ -8125,7 +8125,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>0.4228871083383263</v>
+        <v>0.4177299484805417</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8133,22 +8133,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.2194527050782156</v>
+        <v>0.2213527050782156</v>
       </c>
       <c r="C84">
-        <v>-14.12860377490681</v>
+        <v>-14.40012038969512</v>
       </c>
       <c r="D84">
-        <v>4.307196225093193</v>
+        <v>4.260579610304884</v>
       </c>
       <c r="E84">
-        <v>11.8518</v>
+        <v>12.0767</v>
       </c>
       <c r="F84">
-        <v>18.4418</v>
+        <v>18.6667</v>
       </c>
       <c r="G84">
         <v>0.006</v>
@@ -8169,37 +8169,37 @@
         <v>1.816530612244898</v>
       </c>
       <c r="M84">
-        <v>4.348576440000001</v>
+        <v>4.40160786</v>
       </c>
       <c r="N84">
-        <v>-2.532045827755103</v>
+        <v>-2.585077247755102</v>
       </c>
       <c r="O84">
-        <v>-0.3798068741632655</v>
+        <v>-0.3877615871632653</v>
       </c>
       <c r="P84">
-        <v>-2.152238953591838</v>
+        <v>-2.197315660591837</v>
       </c>
       <c r="Q84">
-        <v>-1.642238953591838</v>
+        <v>-1.687315660591837</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.212290521477645</v>
+        <v>0.2220840815645654</v>
       </c>
       <c r="T84">
-        <v>3.049332369919143</v>
+        <v>3.228704862267328</v>
       </c>
       <c r="U84">
         <v>0.2358</v>
       </c>
       <c r="V84">
-        <v>0.06265949227208126</v>
+        <v>0.06190455863024897</v>
       </c>
       <c r="W84">
-        <v>0.2210248917222433</v>
+        <v>0.2212029050749873</v>
       </c>
       <c r="X84" t="inlineStr">
         <is>
@@ -8207,7 +8207,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>0.4177299484805417</v>
+        <v>0.4126970575349931</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8215,22 +8215,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.2213527050782156</v>
+        <v>0.2232527050782156</v>
       </c>
       <c r="C85">
-        <v>-14.40012038969512</v>
+        <v>-14.6706387489983</v>
       </c>
       <c r="D85">
-        <v>4.260579610304884</v>
+        <v>4.214961251001703</v>
       </c>
       <c r="E85">
-        <v>12.0767</v>
+        <v>12.3016</v>
       </c>
       <c r="F85">
-        <v>18.6667</v>
+        <v>18.8916</v>
       </c>
       <c r="G85">
         <v>0.006</v>
@@ -8251,37 +8251,37 @@
         <v>1.816530612244898</v>
       </c>
       <c r="M85">
-        <v>4.40160786</v>
+        <v>4.454639280000001</v>
       </c>
       <c r="N85">
-        <v>-2.585077247755102</v>
+        <v>-2.638108667755103</v>
       </c>
       <c r="O85">
-        <v>-0.3877615871632653</v>
+        <v>-0.3957163001632655</v>
       </c>
       <c r="P85">
-        <v>-2.197315660591837</v>
+        <v>-2.242392367591838</v>
       </c>
       <c r="Q85">
-        <v>-1.687315660591837</v>
+        <v>-1.732392367591838</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.2220840815645654</v>
+        <v>0.2331018366623507</v>
       </c>
       <c r="T85">
-        <v>3.228704862267328</v>
+        <v>3.430498916159037</v>
       </c>
       <c r="U85">
         <v>0.2358</v>
       </c>
       <c r="V85">
-        <v>0.06190455863024897</v>
+        <v>0.06116759959893647</v>
       </c>
       <c r="W85">
-        <v>0.2212029050749873</v>
+        <v>0.2213766800145708</v>
       </c>
       <c r="X85" t="inlineStr">
         <is>
@@ -8289,7 +8289,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>0.4126970575349931</v>
+        <v>0.4077839973262432</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8297,22 +8297,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.2232527050782155</v>
+        <v>0.2251527050782156</v>
       </c>
       <c r="C86">
-        <v>-14.6706387489983</v>
+        <v>-14.94019057832761</v>
       </c>
       <c r="D86">
-        <v>4.214961251001703</v>
+        <v>4.170309421672391</v>
       </c>
       <c r="E86">
-        <v>12.3016</v>
+        <v>12.5265</v>
       </c>
       <c r="F86">
-        <v>18.8916</v>
+        <v>19.1165</v>
       </c>
       <c r="G86">
         <v>0.006</v>
@@ -8333,37 +8333,37 @@
         <v>1.816530612244898</v>
       </c>
       <c r="M86">
-        <v>4.45463928</v>
+        <v>4.5076707</v>
       </c>
       <c r="N86">
-        <v>-2.638108667755102</v>
+        <v>-2.691140087755102</v>
       </c>
       <c r="O86">
-        <v>-0.3957163001632653</v>
+        <v>-0.4036710131632653</v>
       </c>
       <c r="P86">
-        <v>-2.242392367591837</v>
+        <v>-2.287469074591837</v>
       </c>
       <c r="Q86">
-        <v>-1.732392367591837</v>
+        <v>-1.777469074591837</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>0.2331018366623506</v>
+        <v>0.245588625773174</v>
       </c>
       <c r="T86">
-        <v>3.430498916159034</v>
+        <v>3.65919884390297</v>
       </c>
       <c r="U86">
         <v>0.2358</v>
       </c>
       <c r="V86">
-        <v>0.06116759959893648</v>
+        <v>0.06044798078012546</v>
       </c>
       <c r="W86">
-        <v>0.2213766800145708</v>
+        <v>0.2215463661320464</v>
       </c>
       <c r="X86" t="inlineStr">
         <is>
@@ -8371,7 +8371,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>0.4077839973262432</v>
+        <v>0.4029865385341698</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8379,22 +8379,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.2251527050782156</v>
+        <v>0.2270527050782155</v>
       </c>
       <c r="C87">
-        <v>-14.94019057832761</v>
+        <v>-15.20880627293067</v>
       </c>
       <c r="D87">
-        <v>4.170309421672391</v>
+        <v>4.126593727069332</v>
       </c>
       <c r="E87">
-        <v>12.5265</v>
+        <v>12.7514</v>
       </c>
       <c r="F87">
-        <v>19.1165</v>
+        <v>19.3414</v>
       </c>
       <c r="G87">
         <v>0.006</v>
@@ -8415,37 +8415,37 @@
         <v>1.816530612244898</v>
       </c>
       <c r="M87">
-        <v>4.5076707</v>
+        <v>4.56070212</v>
       </c>
       <c r="N87">
-        <v>-2.691140087755102</v>
+        <v>-2.744171507755102</v>
       </c>
       <c r="O87">
-        <v>-0.4036710131632653</v>
+        <v>-0.4116257261632653</v>
       </c>
       <c r="P87">
-        <v>-2.287469074591837</v>
+        <v>-2.332545781591837</v>
       </c>
       <c r="Q87">
-        <v>-1.777469074591837</v>
+        <v>-1.822545781591837</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>0.245588625773174</v>
+        <v>0.2598592418998292</v>
       </c>
       <c r="T87">
-        <v>3.65919884390297</v>
+        <v>3.920570189896039</v>
       </c>
       <c r="U87">
         <v>0.2358</v>
       </c>
       <c r="V87">
-        <v>0.06044798078012546</v>
+        <v>0.05974509728268215</v>
       </c>
       <c r="W87">
-        <v>0.2215463661320464</v>
+        <v>0.2217121060607435</v>
       </c>
       <c r="X87" t="inlineStr">
         <is>
@@ -8453,7 +8453,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>0.4029865385341698</v>
+        <v>0.3983006485512143</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8461,22 +8461,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.2270527050782155</v>
+        <v>0.2289527050782156</v>
       </c>
       <c r="C88">
-        <v>-15.20880627293067</v>
+        <v>-15.47651496679126</v>
       </c>
       <c r="D88">
-        <v>4.126593727069332</v>
+        <v>4.083785033208744</v>
       </c>
       <c r="E88">
-        <v>12.7514</v>
+        <v>12.9763</v>
       </c>
       <c r="F88">
-        <v>19.3414</v>
+        <v>19.5663</v>
       </c>
       <c r="G88">
         <v>0.006</v>
@@ -8497,37 +8497,37 @@
         <v>1.816530612244898</v>
       </c>
       <c r="M88">
-        <v>4.56070212</v>
+        <v>4.613733540000001</v>
       </c>
       <c r="N88">
-        <v>-2.744171507755102</v>
+        <v>-2.797202927755103</v>
       </c>
       <c r="O88">
-        <v>-0.4116257261632653</v>
+        <v>-0.4195804391632654</v>
       </c>
       <c r="P88">
-        <v>-2.332545781591837</v>
+        <v>-2.377622488591837</v>
       </c>
       <c r="Q88">
-        <v>-1.822545781591837</v>
+        <v>-1.867622488591838</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>0.2598592418998292</v>
+        <v>0.2763253374305853</v>
       </c>
       <c r="T88">
-        <v>3.920570189896039</v>
+        <v>4.222152512195734</v>
       </c>
       <c r="U88">
         <v>0.2358</v>
       </c>
       <c r="V88">
-        <v>0.05974509728268215</v>
+        <v>0.05905837202655935</v>
       </c>
       <c r="W88">
-        <v>0.2217121060607435</v>
+        <v>0.2218740358761373</v>
       </c>
       <c r="X88" t="inlineStr">
         <is>
@@ -8535,7 +8535,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>0.3983006485512143</v>
+        <v>0.3937224801770624</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8543,22 +8543,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.2289527050782156</v>
+        <v>0.2308527050782156</v>
       </c>
       <c r="C89">
-        <v>-15.47651496679126</v>
+        <v>-15.74334459737848</v>
       </c>
       <c r="D89">
-        <v>4.083785033208744</v>
+        <v>4.041855402621517</v>
       </c>
       <c r="E89">
-        <v>12.9763</v>
+        <v>13.2012</v>
       </c>
       <c r="F89">
-        <v>19.5663</v>
+        <v>19.7912</v>
       </c>
       <c r="G89">
         <v>0.006</v>
@@ -8579,37 +8579,37 @@
         <v>1.816530612244898</v>
       </c>
       <c r="M89">
-        <v>4.613733540000001</v>
+        <v>4.666764960000001</v>
       </c>
       <c r="N89">
-        <v>-2.797202927755103</v>
+        <v>-2.850234347755103</v>
       </c>
       <c r="O89">
-        <v>-0.4195804391632654</v>
+        <v>-0.4275351521632654</v>
       </c>
       <c r="P89">
-        <v>-2.377622488591837</v>
+        <v>-2.422699195591838</v>
       </c>
       <c r="Q89">
-        <v>-1.867622488591838</v>
+        <v>-1.912699195591838</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>0.2763253374305853</v>
+        <v>0.2955357822164675</v>
       </c>
       <c r="T89">
-        <v>4.222152512195734</v>
+        <v>4.573998554878713</v>
       </c>
       <c r="U89">
         <v>0.2358</v>
       </c>
       <c r="V89">
-        <v>0.05905837202655935</v>
+        <v>0.05838725416262117</v>
       </c>
       <c r="W89">
-        <v>0.2218740358761373</v>
+        <v>0.2220322854684539</v>
       </c>
       <c r="X89" t="inlineStr">
         <is>
@@ -8617,7 +8617,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>0.3937224801770624</v>
+        <v>0.3892483610841412</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8625,22 +8625,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.2308527050782156</v>
+        <v>0.2327527050782155</v>
       </c>
       <c r="C90">
-        <v>-15.74334459737848</v>
+        <v>-16.00932196644767</v>
       </c>
       <c r="D90">
-        <v>4.041855402621517</v>
+        <v>4.000778033552328</v>
       </c>
       <c r="E90">
-        <v>13.2012</v>
+        <v>13.4261</v>
       </c>
       <c r="F90">
-        <v>19.7912</v>
+        <v>20.0161</v>
       </c>
       <c r="G90">
         <v>0.006</v>
@@ -8661,37 +8661,37 @@
         <v>1.816530612244898</v>
       </c>
       <c r="M90">
-        <v>4.666764960000001</v>
+        <v>4.719796380000001</v>
       </c>
       <c r="N90">
-        <v>-2.850234347755103</v>
+        <v>-2.903265767755103</v>
       </c>
       <c r="O90">
-        <v>-0.4275351521632654</v>
+        <v>-0.4354898651632654</v>
       </c>
       <c r="P90">
-        <v>-2.422699195591838</v>
+        <v>-2.467775902591837</v>
       </c>
       <c r="Q90">
-        <v>-1.912699195591838</v>
+        <v>-1.957775902591838</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>0.2955357822164675</v>
+        <v>0.3182390351452373</v>
       </c>
       <c r="T90">
-        <v>4.573998554878713</v>
+        <v>4.989816605322233</v>
       </c>
       <c r="U90">
         <v>0.2358</v>
       </c>
       <c r="V90">
-        <v>0.05838725416262117</v>
+        <v>0.05773121759899622</v>
       </c>
       <c r="W90">
-        <v>0.2220322854684539</v>
+        <v>0.2221869788901567</v>
       </c>
       <c r="X90" t="inlineStr">
         <is>
@@ -8699,7 +8699,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>0.3892483610841412</v>
+        <v>0.3848747839933081</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8707,22 +8707,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.2327527050782155</v>
+        <v>0.2346527050782156</v>
       </c>
       <c r="C91">
-        <v>-16.00932196644767</v>
+        <v>-16.27447279717102</v>
       </c>
       <c r="D91">
-        <v>4.000778033552328</v>
+        <v>3.960527202828981</v>
       </c>
       <c r="E91">
-        <v>13.4261</v>
+        <v>13.651</v>
       </c>
       <c r="F91">
-        <v>20.0161</v>
+        <v>20.241</v>
       </c>
       <c r="G91">
         <v>0.006</v>
@@ -8743,37 +8743,37 @@
         <v>1.816530612244898</v>
       </c>
       <c r="M91">
-        <v>4.719796380000001</v>
+        <v>4.772827800000001</v>
       </c>
       <c r="N91">
-        <v>-2.903265767755103</v>
+        <v>-2.956297187755103</v>
       </c>
       <c r="O91">
-        <v>-0.4354898651632654</v>
+        <v>-0.4434445781632654</v>
       </c>
       <c r="P91">
-        <v>-2.467775902591837</v>
+        <v>-2.512852609591838</v>
       </c>
       <c r="Q91">
-        <v>-1.957775902591838</v>
+        <v>-2.002852609591838</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>0.3182390351452373</v>
+        <v>0.345482938659761</v>
       </c>
       <c r="T91">
-        <v>4.989816605322233</v>
+        <v>5.488798265854457</v>
       </c>
       <c r="U91">
         <v>0.2358</v>
       </c>
       <c r="V91">
-        <v>0.05773121759899622</v>
+        <v>0.05708975962567404</v>
       </c>
       <c r="W91">
-        <v>0.2221869788901567</v>
+        <v>0.2223382346802661</v>
       </c>
       <c r="X91" t="inlineStr">
         <is>
@@ -8781,7 +8781,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>0.3848747839933081</v>
+        <v>0.3805983975044936</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8789,22 +8789,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.2346527050782156</v>
+        <v>0.2365527050782155</v>
       </c>
       <c r="C92">
-        <v>-16.27447279717102</v>
+        <v>-16.53882178785395</v>
       </c>
       <c r="D92">
-        <v>3.960527202828981</v>
+        <v>3.921078212146047</v>
       </c>
       <c r="E92">
-        <v>13.651</v>
+        <v>13.8759</v>
       </c>
       <c r="F92">
-        <v>20.241</v>
+        <v>20.4659</v>
       </c>
       <c r="G92">
         <v>0.006</v>
@@ -8825,37 +8825,37 @@
         <v>1.816530612244898</v>
       </c>
       <c r="M92">
-        <v>4.772827800000001</v>
+        <v>4.825859220000001</v>
       </c>
       <c r="N92">
-        <v>-2.956297187755103</v>
+        <v>-3.009328607755103</v>
       </c>
       <c r="O92">
-        <v>-0.4434445781632654</v>
+        <v>-0.4513992911632654</v>
       </c>
       <c r="P92">
-        <v>-2.512852609591838</v>
+        <v>-2.557929316591837</v>
       </c>
       <c r="Q92">
-        <v>-2.002852609591838</v>
+        <v>-2.047929316591838</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>0.345482938659761</v>
+        <v>0.3787810429552901</v>
       </c>
       <c r="T92">
-        <v>5.488798265854457</v>
+        <v>6.098664739838286</v>
       </c>
       <c r="U92">
         <v>0.2358</v>
       </c>
       <c r="V92">
-        <v>0.05708975962567404</v>
+        <v>0.05646239962978752</v>
       </c>
       <c r="W92">
-        <v>0.2223382346802661</v>
+        <v>0.2224861661672961</v>
       </c>
       <c r="X92" t="inlineStr">
         <is>
@@ -8863,7 +8863,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>0.3805983975044936</v>
+        <v>0.3764159975319168</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -8871,22 +8871,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.2365527050782155</v>
+        <v>0.2384527050782156</v>
       </c>
       <c r="C93">
-        <v>-16.53882178785395</v>
+        <v>-16.80239266247289</v>
       </c>
       <c r="D93">
-        <v>3.921078212146047</v>
+        <v>3.882407337527116</v>
       </c>
       <c r="E93">
-        <v>13.8759</v>
+        <v>14.1008</v>
       </c>
       <c r="F93">
-        <v>20.4659</v>
+        <v>20.6908</v>
       </c>
       <c r="G93">
         <v>0.006</v>
@@ -8907,37 +8907,37 @@
         <v>1.816530612244898</v>
       </c>
       <c r="M93">
-        <v>4.825859220000001</v>
+        <v>4.878890640000001</v>
       </c>
       <c r="N93">
-        <v>-3.009328607755103</v>
+        <v>-3.062360027755103</v>
       </c>
       <c r="O93">
-        <v>-0.4513992911632654</v>
+        <v>-0.4593540041632654</v>
       </c>
       <c r="P93">
-        <v>-2.557929316591837</v>
+        <v>-2.603006023591837</v>
       </c>
       <c r="Q93">
-        <v>-2.047929316591838</v>
+        <v>-2.093006023591837</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>0.3787810429552901</v>
+        <v>0.4204036733247014</v>
       </c>
       <c r="T93">
-        <v>6.098664739838286</v>
+        <v>6.860997832318073</v>
       </c>
       <c r="U93">
         <v>0.2358</v>
       </c>
       <c r="V93">
-        <v>0.05646239962978752</v>
+        <v>0.05584867789468113</v>
       </c>
       <c r="W93">
-        <v>0.2224861661672961</v>
+        <v>0.2226308817524342</v>
       </c>
       <c r="X93" t="inlineStr">
         <is>
@@ -8945,7 +8945,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>0.3764159975319168</v>
+        <v>0.3723245192978742</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -8953,22 +8953,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.2384527050782156</v>
+        <v>0.2403527050782156</v>
       </c>
       <c r="C94">
-        <v>-16.80239266247289</v>
+        <v>-17.06520821825165</v>
       </c>
       <c r="D94">
-        <v>3.882407337527116</v>
+        <v>3.844491781748359</v>
       </c>
       <c r="E94">
-        <v>14.1008</v>
+        <v>14.3257</v>
       </c>
       <c r="F94">
-        <v>20.6908</v>
+        <v>20.9157</v>
       </c>
       <c r="G94">
         <v>0.006</v>
@@ -8989,37 +8989,37 @@
         <v>1.816530612244898</v>
       </c>
       <c r="M94">
-        <v>4.878890640000001</v>
+        <v>4.931922060000002</v>
       </c>
       <c r="N94">
-        <v>-3.062360027755103</v>
+        <v>-3.115391447755103</v>
       </c>
       <c r="O94">
-        <v>-0.4593540041632654</v>
+        <v>-0.4673087171632655</v>
       </c>
       <c r="P94">
-        <v>-2.603006023591837</v>
+        <v>-2.648082730591838</v>
       </c>
       <c r="Q94">
-        <v>-2.093006023591837</v>
+        <v>-2.138082730591838</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>0.4204036733247014</v>
+        <v>0.4739184837996588</v>
       </c>
       <c r="T94">
-        <v>6.860997832318073</v>
+        <v>7.841140379792085</v>
       </c>
       <c r="U94">
         <v>0.2358</v>
       </c>
       <c r="V94">
-        <v>0.05584867789468113</v>
+        <v>0.05524815447645875</v>
       </c>
       <c r="W94">
-        <v>0.2226308817524342</v>
+        <v>0.2227724851744511</v>
       </c>
       <c r="X94" t="inlineStr">
         <is>
@@ -9027,7 +9027,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>0.3723245192978742</v>
+        <v>0.3683210298430583</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9035,22 +9035,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.2403527050782156</v>
+        <v>0.2422527050782156</v>
       </c>
       <c r="C95">
-        <v>-17.06520821825165</v>
+        <v>-17.3272903704771</v>
       </c>
       <c r="D95">
-        <v>3.844491781748359</v>
+        <v>3.807309629522897</v>
       </c>
       <c r="E95">
-        <v>14.3257</v>
+        <v>14.5506</v>
       </c>
       <c r="F95">
-        <v>20.9157</v>
+        <v>21.1406</v>
       </c>
       <c r="G95">
         <v>0.006</v>
@@ -9071,37 +9071,37 @@
         <v>1.816530612244898</v>
       </c>
       <c r="M95">
-        <v>4.931922060000002</v>
+        <v>4.984953480000001</v>
       </c>
       <c r="N95">
-        <v>-3.115391447755103</v>
+        <v>-3.168422867755103</v>
       </c>
       <c r="O95">
-        <v>-0.4673087171632655</v>
+        <v>-0.4752634301632653</v>
       </c>
       <c r="P95">
-        <v>-2.648082730591838</v>
+        <v>-2.693159437591837</v>
       </c>
       <c r="Q95">
-        <v>-2.138082730591838</v>
+        <v>-2.183159437591837</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>0.4739184837996588</v>
+        <v>0.5452715644329355</v>
       </c>
       <c r="T95">
-        <v>7.841140379792085</v>
+        <v>9.147997109757435</v>
       </c>
       <c r="U95">
         <v>0.2358</v>
       </c>
       <c r="V95">
-        <v>0.05524815447645875</v>
+        <v>0.0546604081522411</v>
       </c>
       <c r="W95">
-        <v>0.2227724851744511</v>
+        <v>0.2229110757577016</v>
       </c>
       <c r="X95" t="inlineStr">
         <is>
@@ -9109,7 +9109,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>0.3683210298430583</v>
+        <v>0.3644027210149408</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9117,22 +9117,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.2422527050782156</v>
+        <v>0.2441527050782156</v>
       </c>
       <c r="C96">
-        <v>-17.3272903704771</v>
+        <v>-17.5886601947391</v>
       </c>
       <c r="D96">
-        <v>3.807309629522897</v>
+        <v>3.770839805260902</v>
       </c>
       <c r="E96">
-        <v>14.5506</v>
+        <v>14.7755</v>
       </c>
       <c r="F96">
-        <v>21.1406</v>
+        <v>21.3655</v>
       </c>
       <c r="G96">
         <v>0.006</v>
@@ -9153,37 +9153,37 @@
         <v>1.816530612244898</v>
       </c>
       <c r="M96">
-        <v>4.984953480000001</v>
+        <v>5.037984900000001</v>
       </c>
       <c r="N96">
-        <v>-3.168422867755103</v>
+        <v>-3.221454287755103</v>
       </c>
       <c r="O96">
-        <v>-0.4752634301632653</v>
+        <v>-0.4832181431632655</v>
       </c>
       <c r="P96">
-        <v>-2.693159437591837</v>
+        <v>-2.738236144591838</v>
       </c>
       <c r="Q96">
-        <v>-2.183159437591837</v>
+        <v>-2.228236144591838</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>0.5452715644329355</v>
+        <v>0.6451658773195228</v>
       </c>
       <c r="T96">
-        <v>9.147997109757435</v>
+        <v>10.97759653170893</v>
       </c>
       <c r="U96">
         <v>0.2358</v>
       </c>
       <c r="V96">
-        <v>0.0546604081522411</v>
+        <v>0.05408503543484908</v>
       </c>
       <c r="W96">
-        <v>0.2229110757577016</v>
+        <v>0.2230467486444626</v>
       </c>
       <c r="X96" t="inlineStr">
         <is>
@@ -9191,7 +9191,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>0.3644027210149408</v>
+        <v>0.360566902898994</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9199,22 +9199,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.2441527050782156</v>
+        <v>0.2460527050782155</v>
       </c>
       <c r="C97">
-        <v>-17.5886601947391</v>
+        <v>-17.84933796676568</v>
       </c>
       <c r="D97">
-        <v>3.770839805260902</v>
+        <v>3.735062033234317</v>
       </c>
       <c r="E97">
-        <v>14.7755</v>
+        <v>15.0004</v>
       </c>
       <c r="F97">
-        <v>21.3655</v>
+        <v>21.5904</v>
       </c>
       <c r="G97">
         <v>0.006</v>
@@ -9235,37 +9235,37 @@
         <v>1.816530612244898</v>
       </c>
       <c r="M97">
-        <v>5.037984900000001</v>
+        <v>5.09101632</v>
       </c>
       <c r="N97">
-        <v>-3.221454287755103</v>
+        <v>-3.274485707755102</v>
       </c>
       <c r="O97">
-        <v>-0.4832181431632655</v>
+        <v>-0.4911728561632653</v>
       </c>
       <c r="P97">
-        <v>-2.738236144591838</v>
+        <v>-2.783312851591837</v>
       </c>
       <c r="Q97">
-        <v>-2.228236144591838</v>
+        <v>-2.273312851591837</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>0.6451658773195228</v>
+        <v>0.7950073466494036</v>
       </c>
       <c r="T97">
-        <v>10.97759653170893</v>
+        <v>13.72199566463616</v>
       </c>
       <c r="U97">
         <v>0.2358</v>
       </c>
       <c r="V97">
-        <v>0.05408503543484908</v>
+        <v>0.05352164964906942</v>
       </c>
       <c r="W97">
-        <v>0.2230467486444626</v>
+        <v>0.2231795950127494</v>
       </c>
       <c r="X97" t="inlineStr">
         <is>
@@ -9273,7 +9273,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>0.360566902898994</v>
+        <v>0.3568109976604628</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9281,22 +9281,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.2460527050782155</v>
+        <v>0.2479527050782155</v>
       </c>
       <c r="C98">
-        <v>-17.84933796676568</v>
+        <v>-18.109343200012</v>
       </c>
       <c r="D98">
-        <v>3.735062033234317</v>
+        <v>3.699956799987997</v>
       </c>
       <c r="E98">
-        <v>15.0004</v>
+        <v>15.2253</v>
       </c>
       <c r="F98">
-        <v>21.5904</v>
+        <v>21.8153</v>
       </c>
       <c r="G98">
         <v>0.006</v>
@@ -9317,37 +9317,37 @@
         <v>1.816530612244898</v>
       </c>
       <c r="M98">
-        <v>5.09101632</v>
+        <v>5.14404774</v>
       </c>
       <c r="N98">
-        <v>-3.274485707755102</v>
+        <v>-3.327517127755102</v>
       </c>
       <c r="O98">
-        <v>-0.4911728561632653</v>
+        <v>-0.4991275691632653</v>
       </c>
       <c r="P98">
-        <v>-2.783312851591837</v>
+        <v>-2.828389558591837</v>
       </c>
       <c r="Q98">
-        <v>-2.273312851591837</v>
+        <v>-2.318389558591837</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>0.7950073466494018</v>
+        <v>1.044743128865869</v>
       </c>
       <c r="T98">
-        <v>13.72199566463613</v>
+        <v>18.29599421951484</v>
       </c>
       <c r="U98">
         <v>0.2358</v>
       </c>
       <c r="V98">
-        <v>0.05352164964906942</v>
+        <v>0.05296988006505839</v>
       </c>
       <c r="W98">
-        <v>0.2231795950127494</v>
+        <v>0.2233097022806592</v>
       </c>
       <c r="X98" t="inlineStr">
         <is>
@@ -9355,7 +9355,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>0.3568109976604628</v>
+        <v>0.353132533767056</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9363,22 +9363,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.2479527050782155</v>
+        <v>0.2498527050782156</v>
       </c>
       <c r="C99">
-        <v>-18.109343200012</v>
+        <v>-18.36869468114911</v>
       </c>
       <c r="D99">
-        <v>3.699956799987997</v>
+        <v>3.665505318850892</v>
       </c>
       <c r="E99">
-        <v>15.2253</v>
+        <v>15.4502</v>
       </c>
       <c r="F99">
-        <v>21.8153</v>
+        <v>22.0402</v>
       </c>
       <c r="G99">
         <v>0.006</v>
@@ -9399,37 +9399,37 @@
         <v>1.816530612244898</v>
       </c>
       <c r="M99">
-        <v>5.14404774</v>
+        <v>5.19707916</v>
       </c>
       <c r="N99">
-        <v>-3.327517127755102</v>
+        <v>-3.380548547755102</v>
       </c>
       <c r="O99">
-        <v>-0.4991275691632653</v>
+        <v>-0.5070822821632653</v>
       </c>
       <c r="P99">
-        <v>-2.828389558591837</v>
+        <v>-2.873466265591837</v>
       </c>
       <c r="Q99">
-        <v>-2.318389558591837</v>
+        <v>-2.363466265591837</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>1.044743128865869</v>
+        <v>1.544214693298804</v>
       </c>
       <c r="T99">
-        <v>18.29599421951484</v>
+        <v>27.44399132927225</v>
       </c>
       <c r="U99">
         <v>0.2358</v>
       </c>
       <c r="V99">
-        <v>0.05296988006505839</v>
+        <v>0.0524293710848027</v>
       </c>
       <c r="W99">
-        <v>0.2233097022806592</v>
+        <v>0.2234371542982035</v>
       </c>
       <c r="X99" t="inlineStr">
         <is>
@@ -9437,7 +9437,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>0.353132533767056</v>
+        <v>0.3495291405653513</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9445,22 +9445,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.2498527050782156</v>
+        <v>0.2517527050782156</v>
       </c>
       <c r="C100">
-        <v>-18.36869468114911</v>
+        <v>-18.6274105035884</v>
       </c>
       <c r="D100">
-        <v>3.665505318850892</v>
+        <v>3.631689496411603</v>
       </c>
       <c r="E100">
-        <v>15.4502</v>
+        <v>15.6751</v>
       </c>
       <c r="F100">
-        <v>22.0402</v>
+        <v>22.2651</v>
       </c>
       <c r="G100">
         <v>0.006</v>
@@ -9481,37 +9481,37 @@
         <v>1.816530612244898</v>
       </c>
       <c r="M100">
-        <v>5.19707916</v>
+        <v>5.25011058</v>
       </c>
       <c r="N100">
-        <v>-3.380548547755102</v>
+        <v>-3.433579967755102</v>
       </c>
       <c r="O100">
-        <v>-0.5070822821632653</v>
+        <v>-0.5150369951632653</v>
       </c>
       <c r="P100">
-        <v>-2.873466265591837</v>
+        <v>-2.918542972591837</v>
       </c>
       <c r="Q100">
-        <v>-2.363466265591837</v>
+        <v>-2.408542972591837</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>1.544214693298804</v>
+        <v>3.042629386597607</v>
       </c>
       <c r="T100">
-        <v>27.44399132927225</v>
+        <v>54.88798265854451</v>
       </c>
       <c r="U100">
         <v>0.2358</v>
       </c>
       <c r="V100">
-        <v>0.0524293710848027</v>
+        <v>0.0518997814778855</v>
       </c>
       <c r="W100">
-        <v>0.2234371542982035</v>
+        <v>0.2235620315275146</v>
       </c>
       <c r="X100" t="inlineStr">
         <is>
@@ -9519,91 +9519,9 @@
         </is>
       </c>
       <c r="Y100">
-        <v>0.3495291405653513</v>
+        <v>0.3459985431859033</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.2517527050782156</v>
-      </c>
-      <c r="C101">
-        <v>-18.6274105035884</v>
-      </c>
-      <c r="D101">
-        <v>3.631689496411603</v>
-      </c>
-      <c r="E101">
-        <v>15.6751</v>
-      </c>
-      <c r="F101">
-        <v>22.2651</v>
-      </c>
-      <c r="G101">
-        <v>0.006</v>
-      </c>
-      <c r="H101">
-        <v>15.9</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>2.326530612244898</v>
-      </c>
-      <c r="K101">
-        <v>0.5099999999999998</v>
-      </c>
-      <c r="L101">
-        <v>1.816530612244898</v>
-      </c>
-      <c r="M101">
-        <v>5.25011058</v>
-      </c>
-      <c r="N101">
-        <v>-3.433579967755102</v>
-      </c>
-      <c r="O101">
-        <v>-0.5150369951632653</v>
-      </c>
-      <c r="P101">
-        <v>-2.918542972591837</v>
-      </c>
-      <c r="Q101">
-        <v>-2.408542972591837</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>3.042629386597607</v>
-      </c>
-      <c r="T101">
-        <v>54.88798265854451</v>
-      </c>
-      <c r="U101">
-        <v>0.2358</v>
-      </c>
-      <c r="V101">
-        <v>0.0518997814778855</v>
-      </c>
-      <c r="W101">
-        <v>0.2235620315275146</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>D2/D</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>0.3459985431859033</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
